--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_03_Dynamics.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_03_Dynamics.xlsx
@@ -1226,11 +1226,6 @@
           <t>অনুভূমিকের সাথে $\beta$ কোণে আনত একটি পাহাড়ের পাদদেশ থেকে পাহাড়ের তল বরাবর ঊর্ধ্বমুখী প্রাসের সর্বাধিক পাল্লার সমীকরণ $R_{\max} = \frac{v_0^2}{g(1 + \sin \beta)}$। প্রমাণ করো যে সর্বাধিক পাল্লার জন্য নিক্ষেপণ কোণ হতে হবে অনুভূমিকের সাথে $\alpha = 45^\circ + \frac{\beta}{2}$। নিচের দিকে নিক্ষেপের ক্ষেত্রে রূপটি কেমন হবে?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>১. হেলানো তলের সমান্তরাল অক্ষ $x'$ এবং লম্ব অক্ষ $y'$ ধরি।
@@ -1284,11 +1279,6 @@
           <t>একটি প্রাসকে অনুভূমিকের সাথে $\theta$ কোণে $v_0$ বেগে নিক্ষেপ করা হলো। সর্বোচ্চ উচ্চতায় প্রাসের গতিপথের বক্রতার ব্যাসার্ধ $\rho_{\text{top}}$ এবং নিক্ষেপ বিন্দুতে বক্রতার ব্যাসার্ধ $\rho_0$-এর অনুপাত নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>১. বক্রতার ব্যাসার্ধের সাধারণ সূত্র: $\rho = \frac{v^2}{a_\perp}$, যেখানে $a_\perp$ হলো বেগের সাথে লম্ব ত্বরণ উপাংশ।
@@ -1338,11 +1328,6 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>একটি প্রাসকে $v_0$ বেগে অনুভূমিকের সাথে $\theta$ কোণে নিক্ষেপ করা হলো। উড্ডয়নকালের কোন মুহূর্তে প্রাসের বেগ ভেক্টর এবং ত্বরণ ভেক্টরের মধ্যবর্তী কোণ $90^\circ$ হবে? যদি $\theta &lt; 45^\circ$ হয়, তবে কি কখনোই এই কোণ $90^\circ$ হতে পারে?</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1398,11 +1383,6 @@
           <t>একই অনুভূমিক পাল্লা $R$-এর জন্য দুটি প্রাসের নিক্ষেপণ কোণ $\theta$ এবং $(90^\circ - \theta)$। যদি তাদের সর্বোচ্চ উচ্চতা যথাক্রমে $h_1$ ও $h_2$ এবং উড্ডয়নকাল $T_1$ ও $T_2$ হয়, তবে প্রমাণ করো যে $R = 4\sqrt{h_1 h_2}$ এবং $R = \frac{1}{2} g T_1 T_2$।</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>১. সর্বোচ্চ উচ্চতাদ্বয়: $h_1 = \frac{v_0^2 \sin^2 \theta}{2g}$, এবং $h_2 = \frac{v_0^2 \sin^2(90^\circ - \theta)}{2g} = \frac{v_0^2 \cos^2 \theta}{2g}$।
@@ -1449,11 +1429,6 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>$m$ ভরের একটি প্রাসকে মূলবিন্দু থেকে অনুভূমিকের সাথে $\theta$ কোণে $v_0$ বেগে নিক্ষেপ করা হলো। নিক্ষেপ বিন্দুর সাপেক্ষে প্রাসের ওপর প্রযুক্ত অভিকর্ষজ টর্ক $\vec{\tau}(t)$ এবং কৌণিক ভরবেগ $\vec{L}(t)$ সময়ের অপেক্ষক হিসেবে নির্ণয় করো। কেন কৌণিক ভরবেগ সংরক্ষিত হয় না?</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1505,11 +1480,6 @@
           <t>মাটিতে স্থাপিত $R$ ব্যাসার্ধের একটি মসৃণ অর্ধ-গোলকের শীর্ষবিন্দু স্পর্শ করে অনুভূমিকভাবে একটি পাথর ছিটকে গেল। পাথরটি গোলকের পৃষ্ঠ স্পর্শ না করে সম্পূর্ণ বাইরে দিয়ে মুক্ত প্রাসের মতো উড়ে যেতে চাইলে শীর্ষবিন্দুতে প্রাসের ন্যূনতম বেগ $v_0$ কত হতে হবে?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>১. অর্ধ-গোলকের শীর্ষবিন্দুতে বক্রতার ব্যাসার্ধ হলো গোলকের নিজস্ব ব্যাসার্ধ $R$।
@@ -1559,11 +1529,6 @@
           <t>একটি প্রাসকে নিক্ষেপ বিন্দু থেকে $d$ দূরত্বে অবস্থিত একটি উল্লম্ব মসৃণ দেয়ালে স্থিতিস্থাপকভাবে ($e = 1$) ধাক্কা খেতে দেওয়া হলো। ধাক্কার পর প্রাসটি পুনরায় নিক্ষেপ বিন্দুতেই ফিরে আসার প্রয়োজনীয় শর্তটি নির্ণয় করো। অনুভূমিক পাল্লা $R$ এবং $d$-এর সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>১. মসৃণ উল্লম্ব দেয়ালে স্থিতিস্থাপক সংঘর্ষে বেগের উলম্ব উপাংশ অপরিবর্তিত থাকে ($v_y' = v_y$) কিন্তু অনুভূমিক উপাংশ বিপরীতমুখী হয় ($v_x' = -v_x$)।
@@ -1610,11 +1575,6 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>একটি অনুভূমিক ট্রলি ধ্রুব অনুভূমিক ত্বরণ $a$-তে চলছে। ট্রলির মেঝে থেকে একজন ব্যক্তি খাড়া ওপরের দিকে ট্রলির সাপেক্ষে $u$ বেগে একটি বল ছুড়ল। বলটি কি পুনরায় ব্যক্তির হাতে এসে পড়বে? বলটি ট্রলির ব্যক্তির পেছনে কত দূরত্বে গিয়ে পড়বে?</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1669,11 +1629,6 @@
           <t>একটি প্রাসের ওপর উল্লম্ব অভিকর্ষ ছাড়াও বাতাসের কারণে একটি ধ্রুব অনুভূমিক ত্বরণ $a_x = -k$ ঋণাত্মক দিকে কাজ করছে। প্রাসের গতিপথ কি এখনও পরাবৃত্ত থাকবে? সর্বোচ্চ উচ্চতা এবং পাল্লার ওপর এর প্রভাব গাণিতিকভাবে দেখাও।</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>১. উল্লম্ব গতি সমীকরণ অপরিবর্তিত থাকে: $y(t) = (v_0 \sin \theta)t - \frac{1}{2}gt^2$। ফলে সর্বোচ্চ উচ্চতা এবং উড্ডয়নকাল $T = \frac{2v_0 \sin \theta}{g}$ একই থাকে।
@@ -1721,11 +1676,6 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>একটি কণা আদি বেগ $v_0$ নিয়ে একটি সান্দ্র তরলে প্রবেশ করল। কণাটির মন্দন বেগের সমানুপাতিক: $a = \frac{dv}{dt} = -kv$ (যেখানে $k$ ধ্রুবক)। কণাটির বেগ সময়ের অপেক্ষক হিসেবে $v(t) = v_0 e^{-kt}$ প্রতিপাদন করো। দেখাও যে কণাটি সম্পূর্ণ থামতে তাত্ত্বিকভাবে অসীম সময় নিলেও এটি একটি সসীম দূরত্ব অতিক্রম করে থামে, যার মান $s_{\max} = \frac{v_0}{k}$।</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1780,11 +1730,6 @@
           <t>উচ্চ বেগে চলমান একটি বস্তুর মন্দন বেগের বর্গের সমানুপাতিক: $\frac{dv}{dt} = -k v^2$। আদি বেগ $v_0$ হলে বেগ এবং দূরত্বের সমীকরণ প্রতিপাদন করো। কণাটির আদি বেগ অর্ধেকে ($v_0/2$) নেমে আসতে কত সময় লাগবে?</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>১. সমাকলন: $\frac{dv}{v^2} = -k dt \implies \int_{v_0}^v v^{-2} dv = -k \int_0^t dt$
@@ -1835,11 +1780,6 @@
           <t>একটি কণা পৃথিবী কেন্দ্র থেকে $r_0$ দূরত্বে স্থির অবস্থা থেকে পৃথিবীর মহাকর্ষীয় টানে মুক্তভাবে পড়ছে ($a = -\frac{GM}{r^2}$)। শক্তি সংরক্ষণ নীতি $v = \sqrt{2GM\left(\frac{1}{r} - \frac{1}{r_0}\right)}$ ব্যবহার করে দেখাও যে কেন সমত্বরণের সমীকরণ এখানে চরম ভুল ফলাফল দেয় এবং পৃথিবীতে আঘাত করার সময় কেপলারের ৩য় সূত্রের সাথে কীভাবে সম্পর্কিত?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>১. মহাকর্ষ বল দূরত্বের বর্গের ব্যস্তানুপাতিক হওয়ায় ত্বরণ ক্রমশ বাড়ে ($a \propto 1/r^2$)।
@@ -1887,11 +1827,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>আধুনিক উচ্চগতির লিফট ও ট্রেনে যাত্রীর স্বাচ্ছন্দ্য রক্ষার জন্য ত্বরণের পরিবর্তনের হার বা 'জার্ক' (Jerk $j = \frac{da}{dt}$) ধ্রুব রাখা হয়। স্থির অবস্থা থেকে যাত্রা করে একটি ট্রেন $t_1$ সময় ধরে ধ্রুব ধনাত্মক জার্ক $+j_0$ এবং পরবর্তী $t_1$ সময় ধরে ধ্রুব ঋণাত্মক জার্ক $-j_0$ অনুভব করে সর্বোচ্চ ত্বরণে পৌঁছে সমবেগে চলতে থাকে। $2t_1$ সময়ে ট্রেনের অর্জিত বেগ এবং অতিক্রান্ত দূরত্ব নির্ণয় করো।</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2004,11 +1939,6 @@
           <t>একই সরল রেললাইনে দুটি ট্রেন একই দিকে চলছে। পেছনের ট্রেনটির দ্রুতি $v_1$ এবং সামনের ট্রেনটির দ্রুতি $v_2$ ($v_1 &gt; v_2$)। যখন তাদের মধ্যবর্তী দূরত্ব $d$, তখন পেছনের ট্রেনের চালক সর্বোচ্চ মন্দন $a$ প্রয়োগ করে ব্রেক চাপলেন। সংঘর্ষ এড়ানোর ন্যূনতম শর্ত প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>১. সামনের ট্রেনের রেফারেন্স ফ্রেমে বিবেচনা করি:
@@ -2060,11 +1990,6 @@
           <t>একটি কণার ত্বরণ $a(t) = a_0 e^{-\lambda t}$। স্থির অবস্থা ($v(0) = 0, x(0) = 0$) থেকে যাত্রা করলে কণাটির প্রান্তিক বেগ (Terminal velocity) এবং অসীম সময়ে অতিক্রান্ত সর্বোচ্চ দূরত্ব কত হবে?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>১. বেগ সমাকলন: $v(t) = \int_0^t a_0 e^{-\lambda t'} dt' = a_0 \left[\frac{e^{-\lambda t'}}{-\lambda}\right]_0^t = \frac{a_0}{\lambda}(1 - e^{-\lambda t})$।
@@ -2111,11 +2036,6 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>একটি কণা মূলবিন্দু থেকে স্থির অবস্থা থেকে যাত্রা শুরু করল যার ত্বরণ $a = k \sqrt{x}$ (যেখানে $k$ একটি ধ্রুবক)। কণাটির বেগ এবং সময়ের সম্পর্ক নির্ণয় করো। দেখাও যে সরণ সময়ের চতুর্থ ঘাতের সমানুপাতিক ($x \propto t^4$)।</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2171,11 +2091,6 @@
           <t>একটি কণার বেগ $v(t) = v_0 \cos(\omega t)$। $t = 0$ থেকে $t = \frac{3\pi}{2\omega}$ সময় ব্যবধানে কণাটির সরণ এবং মোট অতিক্রান্ত দূরত্বের অনুপাত নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>১. সরণ হলো বেগের সরাসরি সমাকলন:
@@ -2228,11 +2143,6 @@
           <t>একটি কণা একটি সরলরেখা বরাবর প্রথম অর্ধ-সময় $v_1$ দ্রুতিতে এবং পরবর্তী অর্ধ-সময় $v_2$ দ্রুতিতে বিপরীত দিকে ফিরে আসে ($v_1 &gt; v_2$)। পুরো যাত্রায় কণাটির গড় বেগ এবং গড় দ্রুতির অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>১. ধরি প্রতিটি অর্ধের সময়কাল $t$। মোট সময় $T = 2t$।
@@ -2282,11 +2192,6 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>ভূমি থেকে $d$ অনুভূমিক ব্যবধানে অবস্থিত দুটি বিন্দু $A$ ও $B$ থেকে একই মুহূর্তে দুটি পাথর নিক্ষেপ করা হলো। $A$ বিন্দু থেকে পাথরটিকে $\theta_1$ কোণে $u_1$ বেগে এবং $B$ বিন্দু থেকে পাথরটিকে $\theta_2$ কোণে $u_2$ বেগে পরস্পরের মুখোমুখি ছোড়া হলো। শূন্যে সংঘর্ষ ঘটার জন্য তাদের আদি বেগের উল্লম্ব উপাংশের সম্পর্ক কী হতে হবে এবং সংঘর্ষের সময় $t_c$ নির্ণয় করো।</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2342,11 +2247,6 @@
           <t>একটি পাথরকে ভূমি থেকে খাড়া ওপরে $u$ বেগে ছুড়ে দেওয়া হলো। ঠিক $\Delta t$ সময় পর অপর একটি পাথরকে একই স্থান থেকে কত বেগে খাড়া ওপরে ছুড়লে তা প্রথম পাথরটিকে তার সর্বোচ্চ উচ্চতায় আঘাত করবে?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>১. প্রথম পাথরের সর্বোচ্চ উচ্চতায় ওঠার সময়: $t_1 = \frac{u}{g}$।
@@ -2395,11 +2295,6 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>নিক্ষেপণ বিন্দু থেকে অনুভূমিক দূরত্ব $d$ এবং উচ্চতা $h$-এ অবস্থিত একটি উল্লম্ব দেয়াল পরিষ্কারভাবে অতিক্রম করতে প্রাসের প্রয়োজনীয় সর্বনিম্ন আদি দ্রুতি $v_{\min}$ কত হতে হবে? নিরাপত্তা পরাবৃত্ত বা ক্যালকুলাস দ্বারা প্রমাণ করো।</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2452,11 +2347,6 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>অনুভূমিকের সাথে $\beta$ কোণে আনত একটি হেলানো তলের পাদদেশ থেকে একটি প্রাসকে তলের সাপেক্ষে $\theta$ কোণে নিক্ষেপ করা হলো। প্রাসটি যদি হেলানো তলের ওপর সম্পূর্ণ লম্বভাবে আঘাত করে, তবে প্রমাণ করো যে $\tan \theta = \frac{1}{2 \tan \beta}$।</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2510,11 +2400,6 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>অনুভূমিকের সাথে $\alpha$ কোণে আনত একটি মসৃণ হেলানো তলের ওপর একটি বলকে মুক্তভাবে $h$ উচ্চতা থেকে ফেলা হলো। তলে প্রথম স্থিতিস্থাপক ধাক্কার ($e = 1$) পর বলটি প্রাসের মতো উড়ে গিয়ে দ্বিতীয়বার তলে আঘাত করে। প্রথম ও দ্বিতীয় আঘাতের মধ্যবর্তী দূরত্ব $L$ কত?</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2572,11 +2457,6 @@
           <t>অনুভূমিক পাল্লা $R = \frac{v_0^2 \sin 2\theta}{g}$। নিক্ষেপণ কোণ $\theta = 45^\circ$-এর কাছাকাছি হলে কোণের সামান্য বিচ্যুতি $d\theta$-র জন্য পাল্লার আপেক্ষিক পরিবর্তন শূন্য হয় কেন? অবকলন দ্বারা প্রমাণ করো এবং সামরিক কামানের গোলার ক্ষেত্রে এর সুবিধা ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>১. ব্যবকলন: $dR = \frac{v_0^2}{g} (2 \cos 2\theta) d\theta$।
@@ -2623,11 +2503,6 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>বিশুদ্ধ পরাবৃত্তের জ্যামিতি অনুসারে প্রাসের ট্রাজেক্টরি $y = x\tan\theta - \frac{gx^2}{2v_0^2\cos^2\theta}$ এর শীর্ষবিন্দু, নাভি (Focus) এবং নিয়ামক রেখার (Directrix) উচ্চতা নির্ণয় করো। দেখাও যে নিয়ামকের উচ্চতা প্রাসের নিক্ষেপণ কোণ $\theta$-র ওপর নির্ভর করে না এবং সর্বদা $Y_{\text{dir}} = \frac{v_0^2}{2g}$ হয়।</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2678,11 +2553,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>মাটি থেকে $h$ উচ্চতার একটি খাড়া পাহাড়ের চূড়া থেকে $v_0$ বেগে একটি পাথর ছুড়লে অনুভূমিক ভূমিতে সর্বোচ্চ পাল্লা পাওয়ার জন্য সর্বোত্তম নিক্ষেপণ কোণ $\sin \theta = \frac{1}{\sqrt{2 + \frac{2gh}{v_0^2}}}$। দেখাও যে $h &gt; 0$ হলে সর্বোত্তম কোণ সর্বদা $45^\circ$-এর চেয়ে কম হয়।</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2734,11 +2604,6 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>একটি কণা সমতলে এমনভাবে চলে যে তার বেগ ভেক্টর $\vec{v} = \alpha y \hat{i} + v_0 \hat{j}$ (যেখানে $\alpha$ ও $v_0$ ধ্রুবক)। কণাটির গতিপথের সমীকরণ $y(x)$ নির্ণয় করো এবং গতিপথের আকৃতি ব্যাখ্যা করো।</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2794,11 +2659,6 @@
           <t>একটি বলকে $h$ উচ্চতা থেকে মেঝেতে ফেলা হলো। মেঝের সাথে বলটির স্থিতিস্থাপকতা গুণাঙ্ক $e$ ($e &lt; 1$)। বলটি সম্পূর্ণ স্থির হওয়া পর্যন্ত মোট কত সময় নেবে এবং মোট কত দূরত্ব অতিক্রম করবে?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>১. প্রথম পতনের সময় $t_0 = \sqrt{\frac{2h}{g}}$ এবং আঘাতের বেগ $v_0 = \sqrt{2gh}$।
@@ -2906,11 +2766,6 @@
           <t>ত্বরণ বনাম অবস্থান ($a-x$) লেখচিত্রের আবদ্ধ ক্ষেত্রফলের ভৌত তাৎপর্য কী? কাজ-শক্তি উপপাদ্য প্রয়োগ করে প্রমাণ করো যে $\int_{x_1}^{x_2} a \, dx = \frac{1}{2}(v_2^2 - v_1^2)$ (একক ভরের গতিশক্তির পরিবর্তন)।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>১. আমরা জানি $a = v \frac{dv}{dx} \implies a \, dx = v \, dv$।
@@ -2959,11 +2814,6 @@
           <t>বেগ-সময় ($v-t$) লেখচিত্রের একটি ইনফ্লেকশন বিন্দুতে (Point of inflection, যেখানে বক্রতা দিক পরিবর্তন করে) ত্বরণের মান সর্বোচ্চ বা সর্বনিম্ন হয় কেন? ক্যালকুলাসের দ্বিতীয় ব্যবকলন দিয়ে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>১. ত্বরণ হলো বেগের ১ম ব্যবকলন: $a(t) = \frac{dv}{dt}$।
@@ -3010,11 +2860,6 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>একটি সরল ছন্দিত স্পন্দকের ফেজ ডায়াগ্রামে বেগ বনাম সরণের লেখচিত্র একটি উপবৃত্ত: $\frac{x^2}{A^2} + \frac{v^2}{v_{\max}^2} = 1$। উপবৃত্তটির ক্ষেত্রফল এবং কৌণিক কম্পাঙ্ক $\omega$-র সম্পর্ক নির্ণয় করো। ফেজ স্পেসের ক্ষেত্রফল $\oint p \, dx$-এর সাথে বোর-সমারফিল্ড কোয়ান্টাইজেশনের সম্পর্ক কী?</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3067,11 +2912,6 @@
           <t>একটি বল মেঝেতে বাউন্স করার সময় বেগ-সময় লেখচিত্রে একটি উল্লম্ব লাফের মতো তীক্ষ্ণ কোণ (Discontinuity in slope) তৈরি হয় যেখানে বেগ মুহূর্তের মধ্যে $+v_0$ থেকে $-v_0$-তে পরিবর্তিত হয়। এই বিন্দুতে ত্বরণ গাণিতিকভাবে কত এবং বলের ঘাত $J = \int F dt$ কীভাবে সংজ্ঞায়িত হয়?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>১. আঘাতের সময়কাল $\Delta t \to 0$ হলে ত্বরণ $a = \frac{\Delta v}{\Delta t} \to \infty$।
@@ -3121,11 +2961,6 @@
           <t>একটি ট্রেনের বেগ-সময় গ্রাফ একটি অধিবৃত্ত: $v(t) = 4t - t^2\text{ m/s}$ ($0 \le t \le 4\text{ s}$)। ট্রেনটির অর্জিত সর্বোচ্চ বেগ এবং ৪ সেকেন্ডে মোট অতিক্রান্ত দূরত্ব নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>১. সর্বোচ্চ বেগের জন্য: $\frac{dv}{dt} = 4 - 2t = 0 \implies t = 2\text{ s}$।
@@ -3174,11 +3009,6 @@
           <t>একটি কণার ত্বরণ-সময় ($a-t$) লেখচিত্র একটি ত্রিভুজ, যার ভূমি $0$ থেকে $6\text{ s}$ এবং শীর্ষ উচ্চতা $t = 3\text{ s}$-এ $a_{\max} = 10\text{ m/s}^2$। কণাটি স্থির অবস্থা থেকে যাত্রা শুরু করলে $6\text{ s}$ শেষে তার চূড়ান্ত বেগ কত হবে?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>১. বেগ বৃদ্ধি হলো $a-t$ লেখচিত্রের আবদ্ধ ক্ষেত্রফল: $\Delta v = \int_0^6 a dt$।
@@ -3226,11 +3056,6 @@
           <t>একটি সরণ-সময় ($x-t$) গ্রাফের ঢাল ঋণাত্মক হতে পারে, কিন্তু একটি মোট অতিক্রান্ত দূরত্ব-সময় ($s-t$) গ্রাফের ঢাল কখনো ঋণাত্মক হতে পারে না কেন? গতিবিদ্যার মৌলিক ধারণার আলোকে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>১. সরণের পরিবর্তনের হার হলো বেগ: $v = \frac{dx}{dt}$। কণা বিপরীত দিকে চললে $v &lt; 0$, ফলে $x-t$ গ্রাফের ঢাল নিম্নমুখী হয়।
@@ -3276,11 +3101,6 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>একটি কণার বেগ $v(t) = v_0 e^{-t/\tau}$। $\ln(v)$ বনাম $t$ লেখচিত্র আঁকলে তার রূপ কেমন হবে এবং লেখচিত্রের ঢাল ও ছেদক থেকে কোন কোন ভৌত রাশি নির্ণয় করা যায়?</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3329,11 +3149,6 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>স্থির অবস্থা থেকে সমত্বরণে পতনশীল কোনো বস্তু পরপর সমান সময় ব্যবধানে (প্রতি $t$ সেকেন্ডে) যে দূরত্ব অতিক্রম করে তার অনুপাত $1 : 3 : 5 : 7 : \dots$ (গ্যালিলিওর বিজোড় সংখ্যার নিয়ম)। ক্যালকুলাস বা $v-t$ গ্রাফের ক্ষেত্রফলের সাহায্যে এই নিয়মটি প্রমাণ করো।</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3388,11 +3203,6 @@
           <t>একটি কণা পোলার স্থানাঙ্কে কার্ডিওইড (Cardioid) কক্ষপথ $r = a(1 - \cos \theta)$ বরাবর এমনভাবে চলছে যে মূলবিন্দুর সাপেক্ষে তার ক্ষেত্রীয় বেগ ধ্রুবক ($r^2 \dot{\theta} = h$)। কণাটির অরীয় ত্বরণ $a_r = \ddot{r} - r\dot{\theta}^2$ নির্ণয় করে দেখাও যে কার্যকর বল দূরত্বের চতুর্থ ঘাতের ব্যস্তানুপাতিক ($F \propto 1/r^4$)।</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>১. বিনেটের কক্ষপথ সমীকরণ: $u = \frac{1}{r}$ বসালে কেন্দ্রীয় বলক্ষেত্রে ত্বরণ $a_r = -h^2 u^2 \left[\frac{d^2 u}{d\theta^2} + u\right]$।
@@ -3441,11 +3251,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>একটি কণা সমদ্রুতি $v$-তে একটি সমকোণী লগারিদমীয় সর্পিল (Logarithmic Spiral $r = a e^{\theta \cot \phi}$) বরাবর চলছে। দেখাও যে কণাটির ব্যাসার্ধ ভেক্টর এবং বেগ ভেক্টরের মধ্যবর্তী কোণ সর্বদা একটি ধ্রুবক $\phi$ এবং কণাটির মূলবিন্দুর দিকে পৌঁছাতে প্রয়োজনীয় সময় সসীম ($t = \frac{r_0}{v \cos \phi}$)।</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3545,11 +3350,6 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>$R$ ব্যাসার্ধের একটি চাকা অনুভূমিক তলে না পিছলে সমদ্রুতি $v_0$-তে গড়াচ্ছে (Pure rolling)। চাকার রিমের ওপর অবস্থিত একটি বিন্দুর গতিপথ একটি সাইক্লয়েড (Cycloid): $x(t) = R(\omega t - \sin \omega t)$, $y(t) = R(1 - \cos \omega t)$। দেখাও যে ভূমির সংস্পর্শে থাকা অবস্থায় বিন্দুটির তাৎক্ষণিক বেগ শূন্য কিন্তু ত্বরণ ঊর্ধ্বমুখী এবং এর মান $\frac{v_0^2}{R}$।</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3608,11 +3408,6 @@
           <t>বিশুদ্ধ ঘূর্ণনে (Rolling without slipping) চাকার কেন্দ্র $v_0$ সমবেগে চলছে। চাকার সর্বোচ্চ শীর্ষবিন্দুর তাৎক্ষণিক বেগ কত? কেন শীর্ষবিন্দুর বেগ কেন্দ্রের বেগের দ্বিগুণ ($2v_0$) হয়?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>১. খাঁটি ঘূর্ণন গতি হলো চলন গতি এবং ঘূর্ণন গতির উপরিপাতন (Superposition)।
@@ -3663,11 +3458,6 @@
           <t>একটি কণার পোলার স্থানাঙ্ক সমীকরণ $r = t^2\text{ m}$ এবং $\theta = 2t\text{ rad}$। $t = 1\text{ s}$ সময়ে কণাটির অরীয় বেগ (Radial velocity) এবং স্পর্শকীয় বেগ (Transverse velocity) নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>১. অরীয় বেগ: $v_r = \dot{r} = \frac{d}{dt}(t^2) = 2t$।
@@ -3715,11 +3505,6 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>$R$ ব্যাসার্ধের একটি অনুভূমিক বাঁকে $v$ দ্রুতিতে চলমান ট্রেনের জন্য লাইনচ্যুত না হয়ে বা চাকার ফ্ল্যাঞ্জে পার্শ্বীয় ঘর্ষণ না তৈরি করে নিরাপদে ঘোরার জন্য রেললাইনের ব্যাংকিং কোণ $\tan \theta = \frac{v^2}{R g}$। যদি ট্রেনের দ্রুতি ডিজাইন গতির চেয়ে দ্বিগুণ ($2v$) হয়, তবে চাকা যেন লাইনচ্যুত না হয় সেজন্য ন্যূনতম ঘর্ষণ গুণাঙ্ক $\mu_s$ কত হতে হবে?</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3773,11 +3558,6 @@
           <t>একটি কণা স্থির অবস্থা থেকে $R$ ব্যাসার্ধের বৃত্তাকার পথে ধ্রুব স্পর্শকীয় ত্বরণ $a_t$-তে ঘুরতে শুরু করল। কত সময় পর কণাটির কেন্দ্রমুখী ত্বরণ তার স্পর্শকীয় ত্বরণের সমান হবে? এই সময়ে কণাটি কত কোণ আবর্তন করবে?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>১. $t$ সময় পর বেগ: $v(t) = a_t t$।
@@ -3827,11 +3607,6 @@
           <t>বৃত্তীয় গতিতে মোট ত্বরণ ভেক্টর $\vec{a} = \vec{a}_t + \vec{a}_c$। যদি মোট ত্বরণ কণার বেগ ভেক্টরের সাথে $45^\circ$ কোণ তৈরি করে, তবে কেন্দ্রমুখী ত্বরণ ও স্পর্শকীয় ত্বরণের সম্পর্ক কী? কণার দ্রুতি কি তখন বৃদ্ধি পাচ্ছে না হ্রাস পাচ্ছে?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>১. বেগ ভেক্টর স্পর্শক বরাবর ক্রিয়া করে। সুতরাং বেগের সাথে মোট ত্বরণের কোণ $\phi$ হলে:
@@ -3879,11 +3654,6 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>একটি সাইক্লয়েড ট্র্যাকে ঘর্ষণহীনভাবে গড়িয়ে পড়া কোনো বস্তুর পতনকাল তার আদি অবস্থানের ওপর নির্ভর করে না (টটক্রোন ধর্ম - Tautochrone property)। বক্ররেখা সমাকলন ব্যবহার করে প্রমাণ করো যে ট্র্যাকের যেকোনো উচ্চতা থেকে ছেড়ে দিলে তলদেশে পৌঁছানোর সময় সর্বদা $T = \pi \sqrt{\frac{R}{g}}$।</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3921,7 +3691,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>উঁচু পাহাড় হতে প্রক্ষেপক নিক্ষেপ</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3934,34 +3704,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(30,25)[size:medium]##
-$h = 80\text{{ m}}$ উঁচু একটি খাড়া পাহাড়ের চূড়া হতে একটি পাথর অনুভূমিকের সাথে $30^\circ$ কোণে ওপরের দিকে $v_0 = 40\text{ m/s}$ বেগে নিক্ষেপ করা হলো। পাথরটি কত সময় পর ভূমিতে আঘাত করবে এবং পাদদেশ থেকে কত অনুভূমিক দূরত্বে গিয়ে পড়বে? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি কণার অবস্থান সমীকরণ সময় $t$-এর সাথে $x(t) = 2t^3 - 9t^2 + 12t - 4$ মিটার অনুসারে পরিবর্তিত হয় ($t$ সেকেন্ডে)। কণাটির বেগ কখন শূন্য হবে এবং বেগ শূন্য হওয়ার মুহূর্তে কণাটির ত্বরণ কত?</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(30,25)[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>উল্লম্ব আদিবেগ $v_{0y} = v_0 \sin 30^\circ = 40 \times 0.5 = 20\text{ m/s}$ (ঊর্ধ্বমুখী)।
-অনুভূমিক বেগ $v_{0x} = 40 \cos 30^\circ = 20\sqrt{3} \approx 34.64\text{ m/s}$।
-উল্লম্ব সরণ $y = -80\text{{ m}}$ (নিম্নমুখী)।
-গতিসূত্র: $y = v_{0y}t - \frac{1}{2}gt^2 \implies -80 = 20t - 4.9t^2 \implies 4.9t^2 - 20t - 80 = 0$।
-দ্বিঘাত সমাধান: $t = \frac{20 + \sqrt{400 - 4(4.9)(-80)}}{2(4.9)} = \frac{20 + \sqrt{400 + 1568}}{9.8} = \frac{20 + 44.36}{9.8} \approx 6.55\text{{ s}}$।
-অনুভূমিক দূরত্ব $x = v_{0x}t = 34.64 \times 6.55 \approx 226.89\text{{ m}}$।</t>
+          <t>বেগ $v(t) = \frac{dx}{dt} = 6t^2 - 18t + 12 = 6(t^2 - 3t + 2) = 6(t-1)(t-2)$। বেগ শূন্য: $v=0 \implies t = 1\text{ s}$ ও $t = 2\text{ s}$। ত্বরণ $a(t) = \frac{dv}{dt} = 12t - 18$। $t = 1\text{ s}$-এ $a(1) = 12(1) - 18 = -6\text{ m/s}^2$। $t = 2\text{ s}$-এ $a(2) = 12(2) - 18 = +6\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>সময় $t = 6.55\text{{ s}}$, অনুভূমিক দূরত্ব $x = 226.9\text{{ m}}$</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>$t = 1\text{ s}$-এ $a = -6\text{ m/s}^2$ এবং $t = 2\text{ s}$-এ $a = +6\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3981,12 +3742,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>আনত তলে প্রাসের পাল্লা ও সর্বোচ্চ দূরত্ব</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TOUGH</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3994,34 +3755,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##
-অনুভূমিকের সাথে $\beta = 30^\circ$ কোণে আনত একটি মসৃণ পাহাড়ের পাদদেশ হতে একটি কামান থেকে পাহাড়ের তল বরাবর $\alpha = 60^\circ$ কোণে (অনুভূমিকের সাথে) $u = 50\text{ m/s}$ বেগে একটি গোলা ছোড়া হলো। পাহাড়ের তলের ওপর গোলাটির পাল্লা $R_{incline}$ কত?</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি গাড়ি $72	ext{ km/h}$ দ্রুতিতে চলছে। চালক হঠাৎ রাস্তায় $50	ext{ m}$ সামনে একটি বাধা দেখতে পেয়ে ব্রেক প্রয়োগ করলেন। চালকের প্রতিক্রিয়া সময় (Reaction time) $0.5	ext{ সেকেন্ড}$ এবং গাড়ির মন্দন $5	ext{ m/s}^2$ হলে গাড়িটি বাধার পূর্বে থামতে পারবে কি?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:incline(30)[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>পাহাড়ের তলের সাপেক্ষে নিক্ষেপণ কোণ $\theta = \alpha - \beta = 60^\circ - 30^\circ = 30^\circ$।
-আনত তলে প্রাসের পাল্লার সূত্র: $R = \frac{u^2}{g\cos^2\beta} [\sin(2\alpha - \beta) - \sin\beta]$।
-অথবা তল বরাবর ত্বরণ $g\sin\beta$ এবং লম্ব ত্বরণ $g\cos\beta$ বিবেচনা করে:
-উড্ডয়নকাল $T = \frac{2u\sin\theta}{g\cos\beta} = \frac{2(50)\sin 30^\circ}{9.8 \cos 30^\circ} = \frac{50}{9.8 \times 0.866} = 5.89\text{{ s}}$।
-পাল্লা $R = (u\cos\theta)T - \frac{1}{2}(g\sin\beta)T^2 = (50\cos 30^\circ)(5.89) - 0.5(9.8\sin 30^\circ)(5.89)^2$
-$= (43.30)(5.89) - 2.45(34.69) = 255.04 - 84.99 = 170.05\text{{ m}}$।</t>
+          <t>বেগ $v_0 = \frac{72 \times 1000}{3600} = 20\text{ m/s}$। প্রতিক্রিয়া সময়ে অতিক্রান্ত দূরত্ব $s_1 = v_0 \times t_r = 20 \times 0.5 = 10\text{ m}$। ব্রেক করার পর মন্দনে অতিক্রান্ত দূরত্ব $s_2 = \frac{v_0^2}{2a} = \frac{20^2}{2 \times 5} = \frac{400}{10} = 40\text{ m}$। মোট থামার দূরত্ব $s = s_1 + s_2 = 10 + 40 = 50.0\text{ m}$। যেহেতু দূরত্ব ঠিক বাধার দূরত্বের সমান, তাই গাড়িটি ঠিক বাধা স্পর্শ করার মুহূর্তে থেমে যাবে।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>$R_{incline} = 170.07\text{{ m}}$</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>মোট থামার দূরত্ব $50.0\text{ m}$, ঠিক বাধার পূর্বে থামবে</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4041,7 +3793,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>অসমত্বরণ ও সমবেগে ধাওয়া-পাল্টা ধাওয়া</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4054,29 +3806,25 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>স্থির অবস্থান হতে একটি বাঘ $a = 3\text{ m/s}^2$ সুষম ত্বরণে যাত্রা শুরু করে $80\text{{ m}}$ সামনে থাকা একটি সমবেগে চলমান হরিণকে তাড়া করল। হরিণটি $15\text{ m/s}$ ধ্রুব বেগে দৌড়ালে বাঘটি কত সময় পর হরিণটিকে ধরতে পারবে এবং এই সময়ে বাঘটি কত দূরত্ব অতিক্রম করবে?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি কণার ত্বরণ $a(t) = (6t - 4)	ext{ m/s}^2$। $t = 0$ সময়ে কণাটির বেগ $v(0) = 2	ext{ m/s}$ এবং অবস্থান $x(0) = 1	ext{ m}$ হলে $t = 3	ext{ সেকেন্ড}$ পরে কণাটির অবস্থান ও বেগ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ধরি $t$ সময় পর বাঘ হরিণকে ধরে।
-বাঘের সরণ $s_1 = \frac{1}{2} a t^2 = 1.5 t^2$।
-হরিণের সরণ $s_2 = v t = 15 t$।
-শর্তানুসারে: $s_1 = s_2 + 80 \implies 1.5 t^2 - 15 t - 80 = 0 \implies 3t^2 - 30t - 160 = 0$।
-$t = \frac{30 + \sqrt{900 - 4(3)(-160)}}{6} = \frac{30 + \sqrt{900 + 1920}}{6} = \frac{30 + \sqrt{2820}}{6} = \frac{30 + 53.10}{6} \approx 13.85\text{{ s}}$।
-বাঘের অতিক্রান্ত দূরত্ব $s_1 = 1.5(13.85)^2 \approx 287.7\text{{ m}}$।</t>
+          <t>$v(t) = \int a dt = \int (6t - 4) dt = 3t^2 - 4t + C_1$। $v(0) = 2 \implies C_1 = 2 \implies v(t) = 3t^2 - 4t + 2$। $t = 3$-এ $v(3) = 3(9) - 4(3) + 2 = 27 - 12 + 2 = 17\text{ m/s}$। $x(t) = \int v dt = t^3 - 2t^2 + 2t + C_2$। $x(0) = 1 \implies C_2 = 1 \implies x(t) = t^3 - 2t^2 + 2t + 1$। $t = 3$-এ $x(3) = 27 - 2(9) + 2(3) + 1 = 27 - 18 + 6 + 1 = 16\text{ m}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>$t = 13.33\text{{ s}}$ (অথবা দ্বিঘাতের ধনাত্মক সমাধান), দূরত্ব $= 266.67\text{{ m}}$</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>বেগ $v(3) = 17\text{ m/s}$, অবস্থান $x(3) = 16\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4096,44 +3844,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 4</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $45^\circ$ কোণে $28\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি ট্রেন স্থির অবস্থা থেকে $2	ext{ m/s}^2$ সুষম ত্বরণে যাত্রা শুরু করল। ঠিক একই মুহূর্তে একটি গাড়ি ট্রেনের $100	ext{ m}$ পিছন থেকে $30	ext{ m/s}$ সুষম দ্রুতিতে ট্রেনটিকে তাড়া করল। গাড়িটি কখন এবং ট্রেনটির যাত্রাবিন্দু হতে কত দূরত্বে ট্রেনটিকে অতিক্রম করবে?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{28^2 \sin^2(45^\circ)}{2(9.8)} = 20.0\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.04\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 80.0\text{ m}$।</t>
+          <t>ট্রেনের সরণ $s_T = \frac{1}{2}a t^2 = t^2$। গাড়ির সরণ $s_C = v t = 30t$। গাড়ি ট্রেনকে ধরতে হলে: $s_C = 100 + s_T \implies 30t = 100 + t^2 \implies t^2 - 30t + 100 = 0$। দ্বিঘাত সমীকরণ হতে: $t = \frac{30 \pm \sqrt{900 - 400}}{2} = \frac{30 \pm \sqrt{500}}{2} = \frac{30 \pm 22.36}{2} \implies t_1 = 3.82\text{ s}$ এবং $t_2 = 26.18\text{ s}$। প্রথমবার অতিক্রমের সময় $t = 3.82\text{ s}$। যাত্রাবিন্দু হতে দূরত্ব $s_T = (3.82)^2 \approx 14.6\text{ m}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>$H = 20.0\text{ m}, T = 4.04\text{ s}, R = 80.0\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>$t = 4.38\text{ s}$ পরে যাত্রাবিন্দুর $19.2\text{ m}$ সামনে</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4153,39 +3895,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 5</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $50^\circ$ কোণে $30\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি কণা সরলরেখায় চলছে যার বেগ দূরত্বের ওপর নির্ভর করে: $v = \sqrt{49 - 9x^2}	ext{ m/s}$। কণাটির ত্বরণকে দূরত্বের অপেক্ষক হিসেবে প্রকাশ কর এবং $x = 2	ext{ m}$ অবস্থানে ত্বরণ কত?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{30^2 \sin^2(50^\circ)}{2(9.8)} = 26.95\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.69\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 90.44\text{ m}$।</t>
+          <t>$v^2 = 49 - 9x^2$। উভয়পক্ষে $x$-এর সাপেক্ষে ব্যবকলন করে: $2v \frac{dv}{dx} = -18x \implies v\frac{dv}{dx} = -9x$। যেহেতু ত্বরণ $a = v\frac{dv}{dx}$, সুতরাং $a(x) = -9x$। $x = 2\text{ m}$-এ ত্বরণ $a = -9(2) = -18\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>$H = 26.95\text{ m}, T = 4.69\text{ s}, R = 90.44\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>$a(x) = -9x$, $x = 2\text{ m}$-এ $a = -18\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4205,39 +3946,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 6</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $55^\circ$ কোণে $32\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=4][size:small]##
+একটি লিফট $a = 1.8	ext{ m/s}^2$ সুষম ত্বরণে খাড়া উপরে উঠছে। লিফটের মেঝে থেকে $2.5	ext{ m}$ উঁচুতে থাকা সিলিং থেকে একটি বল ছুটে মেঝেতে পড়ল ($g = 9.8	ext{ ms}^{-2}$)। বলটি মেঝেকে আঘাত করতে কত সেকেন্ড সময় নিবে?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{32^2 \sin^2(55^\circ)}{2(9.8)} = 35.06\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 5.35\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 98.19\text{ m}$।</t>
+          <t>লিফটের সাপেক্ষে বলটির আপেক্ষিক নিম্নমুখী ত্বরণ $a_{rel} = g + a = 9.8 + 1.8 = 11.6\text{ m/s}^2$। উচ্চতা $h = 2.5\text{ m}$। $h = \frac{1}{2}a_{rel} t^2 \implies 2.5 = \frac{1}{2}(11.6) t^2 = 5.8 t^2 \implies t = \sqrt{\frac{2.5}{5.8}} = \sqrt{0.431} \approx 0.656\text{ s}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>$H = 35.06\text{ m}, T = 5.35\text{ s}, R = 98.19\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>সময় $t = 0.656\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4257,39 +3997,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 7</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $60^\circ$ কোণে $34\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##
+একটি বুলেট কোনো কাঠের তক্তায় প্রবেশ করে $3	ext{ cm}$ দূরত্ব অতিক্রম করার পর তার আদি বেগের অর্ধেক হারায়। তক্তাটি বুলেটের ওপর ধ্রুব প্রতিরোধী মন্দন বল প্রয়োগ করলে বুলেটটি তক্তার অভ্যন্তরে আর কত দূরত্ব অতিক্রম করে সম্পূর্ণরূপে থেমে যাবে?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{34^2 \sin^2(60^\circ)}{2(9.8)} = 44.23\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.01\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 102.16\text{ m}$।</t>
+          <t>আদি বেগ $u$, বেগ অর্ধেক হলে বেগ $v_1 = u/2$। $v^2 = u^2 - 2as \implies (u/2)^2 = u^2 - 2a(3) \implies \frac{u^2}{4} = u^2 - 6a \implies 6a = \frac{3}{4}u^2 \implies a = \frac{u^2}{8}$। সম্পূর্ণ থামার জন্য: $0 = (u/2)^2 - 2a s' \implies \frac{u^2}{4} = 2\left(\frac{u^2}{8}\right)s' = \frac{u^2}{4}s' \implies s' = 1.0\text{ cm}$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>$H = 44.23\text{ m}, T = 6.01\text{ s}, R = 102.16\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>আর $1.0\text{ cm}$ অতিক্রম করে থামবে</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4309,44 +4048,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 8</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $25^\circ$ কোণে $36\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি বস্তু সমত্বরণে সরলরেখায় চলে ৫ম সেকেন্ডে $25	ext{ m}$ এবং ৮ম সেকেন্ডে $34	ext{ m}$ দূরত্ব অতিক্রম করে। বস্তুটির আদি বেগ এবং ত্বরণ কত?</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{36^2 \sin^2(25^\circ)}{2(9.8)} = 11.81\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.1\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 101.31\text{ m}$।</t>
+          <t>$t$-তম সেকেন্ডে অতিক্রান্ত দূরত্ব: $s_t = u + \frac{1}{2}a(2t-1)$। ৫ম সেকেন্ডে: $25 = u + \frac{1}{2}a(9) = u + 4.5a$। ৮ম সেকেন্ডে: $34 = u + \frac{1}{2}a(15) = u + 7.5a$। বিয়োগ করে: $3a = 9 \implies a = 3.0\text{ m/s}^2$। $u = 25 - 4.5(3) = 25 - 13.5 = 11.5\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>$H = 11.81\text{ m}, T = 3.1\text{ s}, R = 101.31\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>আদি বেগ $u = 11.5\text{ m/s}$, ত্বরণ $a = 3.0\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4366,39 +4099,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 9</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $30^\circ$ কোণে $38\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:triangle[a=3,b=4,c=5][size:small]##
+একটি গাড়ি স্থির অবস্থা হতে যাত্রা শুরু করে প্রথম $t_1$ সময় ধরে সুষম ত্বরণ $a_1$ নিয়ে চলে এবং পরবর্তী $t_2$ সময়ে সুষম মন্দন $a_2$ নিয়ে থেমে যায়। যাত্রা পথের মোট সময় $T = 30	ext{ s}$ এবং মোট দূরত্ব $600	ext{ m}$ হলে গাড়িটির অর্জিত সর্বোচ্চ বেগ কত ছিল?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[a=3,b=4,c=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{38^2 \sin^2(30^\circ)}{2(9.8)} = 18.42\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.88\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 127.61\text{ m}$।</t>
+          <t>$v-t$ লেখচিত্র একটি ত্রিভুজ গঠন করে যার ভূমি $T = 30\text{ s}$ এবং উচ্চতা $v_{\max}$। ত্রিভুজের ক্ষেত্রফলই মোট অতিক্রান্ত দূরত্ব: $s = \frac{1}{2} \times T \times v_{\max} \implies 600 = \frac{1}{2} \times 30 \times v_{\max} = 15 v_{\max} \implies v_{\max} = \frac{600}{15} = 40.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>$H = 18.42\text{ m}, T = 3.88\text{ s}, R = 127.61\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>সর্বোচ্চ বেগ $v_{\max} = 40.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4418,39 +4150,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 10</t>
+          <t>সরলরেখায় গতি ও পরিবর্তনশীল ত্বরণ (1D Kinematics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $35^\circ$ কোণে $40\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=4][size:small]##
+একটি বেলুন ভূপৃষ্ঠ হতে $1.25	ext{ m/s}^2$ সুষম ত্বরণে খাড়া উপরে উঠছে। $8	ext{ সেকেন্ড}$ পর বেলুন হতে একটি পাথর ফেলে দেওয়া হলো ($g = 9.8	ext{ ms}^{-2}$)। পাথরটি ভূপৃষ্ঠে পৌঁছাতে মোট কত সময় নিবে?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{40^2 \sin^2(35^\circ)}{2(9.8)} = 26.86\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.68\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 153.42\text{ m}$।</t>
+          <t>$8\text{ s}$ পরে বেলুনের উচ্চতা $h = \frac{1}{2}a t^2 = \frac{1}{2}(1.25)(64) = 40\text{ m}$। বেলুনের বেগ (পাথরের আদি উর্ধ্বমুখী বেগ) $u = at = 1.25 \times 8 = 10\text{ m/s}$। পাথর পতনের জন্য: $-h = ut - \frac{1}{2}g t^2 \implies -40 = 10t - 4.9t^2 \implies 4.9t^2 - 10t - 40 = 0$। $t = \frac{10 \pm \sqrt{100 - 4(4.9)(-40)}}{9.8} = \frac{10 \pm \sqrt{100 + 784}}{9.8} = \frac{10 + 29.73}{9.8} \approx 4.05\text{ s}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>$H = 26.86\text{ m}, T = 4.68\text{ s}, R = 153.42\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>সময় $t \approx 4.36\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4470,39 +4201,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 11</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $40^\circ$ কোণে $42\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রক্ষেপককে $u = 40	ext{ m/s}$ আদি বেগে অনুভূমিকের সাথে $	heta = 30^\circ$ কোণে নিক্ষেপ করা হলো ($g = 9.8	ext{ ms}^{-2}$)। সর্বোচ্চ উচ্চতা, বিচরণকাল এবং আনুভূমিক পাল্লা নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{42^2 \sin^2(40^\circ)}{2(9.8)} = 37.19\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 5.51\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 177.27\text{ m}$।</t>
+          <t>উল্লম্ব বেগ $u_y = 40\sin 30^\circ = 20\text{ m/s}$। অনুভূমিক বেগ $u_x = 40\cos 30^\circ = 34.64\text{ m/s}$। $H = \frac{u_y^2}{2g} = \frac{400}{19.6} = 20.41\text{ m}$। $T = \frac{2u_y}{g} = \frac{40}{9.8} = 4.08\text{ s}$। $R = u_x T = 34.64 \times 4.08 = 141.39\text{ m}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>$H = 37.19\text{ m}, T = 5.51\text{ s}, R = 177.27\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>$H = 20.41\text{ m}, T = 4.08\text{ s}, R = 141.39\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4522,44 +4252,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 12</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $45^\circ$ কোণে $44\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের বিচরণকালে তার অনুভূমিক পাল্লা সর্বোচ্চ উচ্চতার চারগুণ ($R = 4H$)। প্রাসটির নিক্ষেপণ কোণ $	heta$ কত?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{44^2 \sin^2(45^\circ)}{2(9.8)} = 49.39\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.35\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 197.55\text{ m}$।</t>
+          <t>$R = \frac{u^2 \sin 2\theta}{g} = \frac{2u^2\sin\theta\cos\theta}{g}$। $H = \frac{u^2\sin^2\theta}{2g}$। $R = 4H \implies \frac{2u^2\sin\theta\cos\theta}{g} = 4\left(\frac{u^2\sin^2\theta}{2g}\right) = \frac{2u^2\sin^2\theta}{g} \implies \cos\theta = \sin\theta \implies \tan\theta = 1 \implies \theta = 45^\circ$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>$H = 49.39\text{ m}, T = 6.35\text{ s}, R = 197.55\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>$\theta = 45^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4579,39 +4303,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 13</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $50^\circ$ কোণে $46\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের গতিপথের সমীকরণ $y = \sqrt{3}x - rac{g x^2}{2}$ হলে প্রাসটির নিক্ষেপণ কোণ এবং আদি দ্রুতি নির্ণয় কর ($g = 9.8	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{46^2 \sin^2(50^\circ)}{2(9.8)} = 63.35\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 7.19\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 212.64\text{ m}$।</t>
+          <t>প্রাসের আদর্শ সমীকরণ $y = x\tan\theta - \frac{g x^2}{2u^2\cos^2\theta}$। তুলনা করে: $\tan\theta = \sqrt{3} \implies \theta = 60^\circ$। আবার $\frac{g}{2u^2\cos^2\theta} = \frac{g}{2} \implies u^2\cos^2 60^\circ = 1 \implies u^2(0.5)^2 = 1 \implies 0.25u^2 = 1 \implies u^2 = 4 \implies u = 2\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>$H = 63.35\text{ m}, T = 7.19\text{ s}, R = 212.64\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>$\theta = 60^\circ, u = 2\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4631,39 +4354,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 14</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $55^\circ$ কোণে $48\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি ফুটবলকে অনুভূমিকের সাথে $45^\circ$ কোণে $20	ext{ m/s}$ বেগে কিক করা হলো। গতিপথের শীর্ষবিন্দুতে প্রক্ষেপকটির বক্রতার ব্যাসার্ধ (Radius of Curvature) কত?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{48^2 \sin^2(55^\circ)}{2(9.8)} = 78.88\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 8.02\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 220.92\text{ m}$।</t>
+          <t>শীর্ষবিন্দুতে কেবল অনুভূমিক বেগ বিদ্যমান: $v = u\cos 45^\circ = 20 \times \frac{1}{\sqrt{2}} = 10\sqrt{2}\text{ m/s}$। শীর্ষবিন্দুতে কেন্দ্রমুখী ত্বরণ হলো সম্পূর্ণ অভিকর্ষজ ত্বরণ $g$। $g = \frac{v^2}{\rho} \implies \rho = \frac{v^2}{g} = \frac{(10\sqrt{2})^2}{9.8} = \frac{200}{9.8} \approx 20.41\text{ m}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>$H = 78.88\text{ m}, T = 8.02\text{ s}, R = 220.92\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>$\rho = 20.41\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4683,39 +4405,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 15</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $60^\circ$ কোণে $20\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একই আদি দ্রুতি $u$-তে দুটি ভিন্ন নিক্ষেপণ কোণ $	heta$ এবং $(90^\circ - 	heta)$-তে কোনো প্রাসের পাল্লা একই ($R$) হয়। যদি তাদের অর্জিত সর্বোচ্চ উচ্চতা যথাক্রমে $h_1$ এবং $h_2$ হয়, তবে প্রমাণ কর যে $R = 4\sqrt{h_1 h_2}$।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{20^2 \sin^2(60^\circ)}{2(9.8)} = 15.31\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.53\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 35.35\text{ m}$।</t>
+          <t>$h_1 = \frac{u^2\sin^2\theta}{2g}$ এবং $h_2 = \frac{u^2\sin^2(90^\circ-\theta)}{2g} = \frac{u^2\cos^2\theta}{2g}$। গুণ করে: $h_1 h_2 = \frac{u^4 \sin^2\theta\cos^2\theta}{4g^2} = \frac{(u^2 \cdot 2\sin\theta\cos\theta)^2}{16g^2} = \frac{R^2}{16} \implies R^2 = 16 h_1 h_2 \implies R = 4\sqrt{h_1 h_2}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>$H = 15.31\text{ m}, T = 3.53\text{ s}, R = 35.35\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>$R = 4\sqrt{h_1 h_2}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4735,44 +4456,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 16</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $25^\circ$ কোণে $22\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের আদি দ্রুতি $u = 50	ext{ m/s}$ এবং নিক্ষেপণ কোণ $	heta = 53^\circ$ ($\sin 53^\circ = 0.8, \cos 53^\circ = 0.6$)। নিক্ষেপের $2	ext{ সেকেন্ড}$ পর প্রাসের বেগ ভেক্টর, দ্রুতি এবং অনুভূমিকের সাথে উৎপন্ন কোণ কত? ($g = 10	ext{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{22^2 \sin^2(25^\circ)}{2(9.8)} = 4.41\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 1.9\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 37.83\text{ m}$।</t>
+          <t>$v_x = u\cos 53^\circ = 50(0.6) = 30\text{ m/s}$। $v_y = u\sin 53^\circ - gt = 50(0.8) - 10(2) = 40 - 20 = 20\text{ m/s}$। বেগ ভেক্টর $\vec{v} = 30\hat{i} + 20\hat{j}\text{ m/s}$। দ্রুতি $v = \sqrt{30^2 + 20^2} = \sqrt{900+400} = \sqrt{1300} \approx 36.06\text{ m/s}$। দিক $\tan\alpha = \frac{v_y}{v_x} = \frac{20}{30} = \frac{2}{3} \implies \alpha = 33.69^\circ$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>$H = 4.41\text{ m}, T = 1.9\text{ s}, R = 37.83\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>$\vec{v} = 30\hat{i} + 20\hat{j}\text{ m/s}, |\vec{v}| = 36.06\text{ m/s}, \alpha \approx 33.69^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4792,39 +4507,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 17</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $30^\circ$ কোণে $24\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি বন্দুকের গুলি অনুভূমিকের সাথে $	heta$ কোণে ছুঁড়লে তা সর্বোচ্চ $R_{\max} = 1.6	ext{ km}$ দূরত্বে আঘাত হানতে পারে। গুলিটির আদি দ্রুতি কত? একই আদি দ্রুতিতে $1	ext{ km}$ দূরে থাকা কোনো লক্ষ্যবস্তুতে আঘাত করতে হলে সম্ভাব্য দুটি নিক্ষেপণ কোণ কত?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{24^2 \sin^2(30^\circ)}{2(9.8)} = 7.35\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 2.45\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 50.9\text{ m}$।</t>
+          <t>$R_{\max} = \frac{u^2}{g} \implies 1600 = \frac{u^2}{9.8} \implies u = \sqrt{1600 \times 9.8} = \sqrt{15680} \approx 125.22\text{ m/s}$। $R = \frac{u^2\sin 2\theta}{g} \implies 1000 = 1600\sin 2\theta \implies \sin 2\theta = \frac{1000}{1600} = 0.625 \implies 2\theta = \sin^{-1}(0.625) \approx 38.68^\circ \implies \theta_1 = 19.34^\circ$ এবং $\theta_2 = 90^\circ - 19.34^\circ = 70.66^\circ$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>$H = 7.35\text{ m}, T = 2.45\text{ s}, R = 50.9\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>$u = 125.22\text{ m/s}$, কোণদ্বয় $19.34^\circ$ এবং $70.66^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4844,39 +4558,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 18</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $35^\circ$ কোণে $26\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি কণা অনুভূমিক তলের সাথে $	heta$ কোণে প্রক্ষিপ্ত হলো। নিক্ষেপের $t_1$ ও $t_2$ সময়ে কণাটি ভূমি হতে একই উচ্চতা $h$-এ অবস্থান করে। দেখাও যে $t_1 + t_2 = T$ (মোট বিচরণকাল) এবং উচ্চতা $h = rac{1}{2}g t_1 t_2$।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{26^2 \sin^2(35^\circ)}{2(9.8)} = 11.35\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.04\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 64.82\text{ m}$।</t>
+          <t>উল্লম্ব সরণ $h = (u\sin\theta)t - \frac{1}{2}g t^2 \implies \frac{1}{2}g t^2 - (u\sin\theta)t + h = 0$। মূলদ্বয়ের যোগফল: $t_1 + t_2 = \frac{u\sin\theta}{g/2} = \frac{2u\sin\theta}{g} = T$। মূলদ্বয়ের গুণফল: $t_1 t_2 = \frac{h}{g/2} \implies h = \frac{1}{2}g t_1 t_2$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>$H = 11.35\text{ m}, T = 3.04\text{ s}, R = 64.82\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$t_1 + t_2 = T, h = \frac{1}{2}g t_1 t_2$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4896,39 +4609,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 19</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $40^\circ$ কোণে $28\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের অনুভূমিক বেগ $15	ext{ m/s}$ এবং উল্লম্ব আদি বেগ $20	ext{ m/s}$। নিক্ষেপের কত সময় পর কণাটির বেগ ভেক্টর অনুভূমিকের সাথে $30^\circ$ কোণ উৎপন্ন করবে? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{28^2 \sin^2(40^\circ)}{2(9.8)} = 16.53\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.67\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 78.78\text{ m}$।</t>
+          <t>অনুভূমিক বেগ ধ্রুব: $v_x = 15\text{ m/s}$। কোণ $30^\circ$ হলে: $\tan 30^\circ = \frac{|v_y|}{v_x} \implies \frac{1}{\sqrt{3}} = \frac{|20 - 10t|}{15} \implies |20 - 10t| = \frac{15}{\sqrt{3}} = 5\sqrt{3} \approx 8.66$। ধনাত্মক মান: $20 - 10t = 8.66 \implies 10t = 11.34 \implies t = 1.134\text{ s}$। ঋণাত্মক মান (নামার সময়): $10t - 20 = 8.66 \implies 10t = 28.66 \implies t = 2.866\text{ s}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>$H = 16.53\text{ m}, T = 3.67\text{ s}, R = 78.78\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>$t = 1.13\text{ s}$ (উর্ধমুখী) অথবা $t = 2.87\text{ s}$ (নিম্নমুখী)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4948,44 +4660,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 20</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $45^\circ$ কোণে $30\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের গতিশক্তিতে পরিবর্তন বিশ্লেষণ কর। অনুভূমিকের সাথে $60^\circ$ কোণে প্রক্ষিপ্ত একটি প্রাসের নিক্ষেপণের মুহূর্তে গতিশক্তি $E_0$ হলে সর্বোচ্চ উচ্চতায় গতিশক্তি কত?</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{30^2 \sin^2(45^\circ)}{2(9.8)} = 22.96\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.33\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 91.84\text{ m}$।</t>
+          <t>আদি গতিশক্তি $E_0 = \frac{1}{2}m u^2$। শীর্ষবিন্দুতে কেবল অনুভূমিক বেগ বিদ্যমান: $v = u\cos 60^\circ = \frac{u}{2}$। শীর্ষবিন্দুতে গতিশক্তি $E = \frac{1}{2}m v^2 = \frac{1}{2}m \left(\frac{u}{2}\right)^2 = \frac{1}{4}\left(\frac{1}{2}m u^2\right) = \frac{E_0}{4}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>$H = 22.96\text{ m}, T = 4.33\text{ s}, R = 91.84\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>$E = \frac{E_0}{4} = 0.25E_0$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5005,39 +4711,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 21</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $50^\circ$ কোণে $32\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের আনুভূমিক পাল্লা $R = 200	ext{ m}$ এবং বিচরণকাল $T = 5	ext{ s}$ হলে প্রাসটির নিক্ষেপণ কোণ এবং আদি বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{32^2 \sin^2(50^\circ)}{2(9.8)} = 30.66\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 5.0\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 102.9\text{ m}$।</t>
+          <t>$v_x = \frac{R}{T} = \frac{200}{5} = 40\text{ m/s}$। বিচরণকাল $T = \frac{2v_y}{g} \implies v_y = \frac{g T}{2} = \frac{9.8 \times 5}{2} = 24.5\text{ m/s}$। $\tan\theta = \frac{v_y}{v_x} = \frac{24.5}{40} = 0.6125 \implies \theta = 31.49^\circ$। আদি বেগ $u = \sqrt{v_x^2 + v_y^2} = \sqrt{40^2 + 24.5^2} = \sqrt{1600 + 600.25} = \sqrt{2200.25} \approx 46.91\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>$H = 30.66\text{ m}, T = 5.0\text{ s}, R = 102.9\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>$\theta = 31.43^\circ, u = 46.88\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5057,39 +4762,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 22</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $55^\circ$ কোণে $34\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের সর্বোচ্চ অনুভূমিক পাল্লা $R_{\max} = 100	ext{ m}$ হলে প্রাসটির অর্জিত সর্বোচ্চ উচ্চতা $H_{\max}$ কত?</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{34^2 \sin^2(55^\circ)}{2(9.8)} = 39.58\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 5.68\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 110.85\text{ m}$।</t>
+          <t>সর্বোচ্চ পাল্লার জন্য $\theta = 45^\circ$, $R_{\max} = \frac{u^2}{g} = 100\text{ m}$। অর্জিত সর্বোচ্চ উচ্চতা যখন $\theta = 90^\circ$ খাড়া উপরে ছোঁড়া হয়: $H_{\max} = \frac{u^2}{2g} = \frac{R_{\max}}{2} = \frac{100}{2} = 50.0\text{ m}$। (অথবা $\theta=45^\circ$-তে উচ্চতা $H = \frac{R_{\max}}{4} = 25\text{ m}$)।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>$H = 39.58\text{ m}, T = 5.68\text{ s}, R = 110.85\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$H_{\max} = 50.0\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5109,39 +4813,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 23</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $60^\circ$ কোণে $36\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি ক্রিকেট বলকে $28	ext{ m/s}$ দ্রুতিতে অনুভূমিকের সাথে $30^\circ$ কোণে ব্যাট দিয়ে আঘাত করা হলো। বলটি মাটি থেকে $1.5	ext{ m}$ উঁচুতে থাকা সীমানা প্রাচীর স্পর্শ না করে ওভারবাউন্ডারি হবে কি, যদি বাউন্ডারি প্রাচীরটি ব্যাটসম্যান হতে $60	ext{ m}$ দূরে থাকে?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{36^2 \sin^2(60^\circ)}{2(9.8)} = 49.59\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.36\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 114.53\text{ m}$।</t>
+          <t>$u_x = 28\cos 30^\circ = 24.25\text{ m/s}$, $u_y = 28\sin 30^\circ = 14\text{ m/s}$। প্রাচীরে পৌঁছাতে সময় $t = \frac{60}{24.25} = 2.474\text{ s}$। উল্লম্ব উচ্চতা $y = u_y t - \frac{1}{2}g t^2 = 14(2.474) - 4.9(2.474)^2 = 34.64 - 29.99 = 4.65\text{ m}$। যেহেতু প্রাচীরের উচ্চতা $1.5\text{ m}$, সুতরাং বলটি প্রাচীরের $3.15\text{ m}$ উপর দিয়ে গিয়ে ছক্কা হবে।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>$H = 49.59\text{ m}, T = 6.36\text{ s}, R = 114.53\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>বলটির উচ্চতা $h = 4.67\text{ m} &gt; 1.5\text{ m}$, ওভারবাউন্ডারি হবে</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5161,44 +4864,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 24</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $25^\circ$ কোণে $38\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের দুটি ভিন্ন নিক্ষেপণ কোণে সমান অনুভূমিক পাল্লা অর্জিত হয়। যদি এই দুই ক্ষেত্রে উড্ডয়নকাল $t_1$ ও $t_2$ হয়, তবে প্রমাণ কর যে $t_1 t_2 = rac{2R}{g}$।</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{38^2 \sin^2(25^\circ)}{2(9.8)} = 13.16\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.28\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 112.87\text{ m}$।</t>
+          <t>$t_1 = \frac{2u\sin\theta}{g}$, $t_2 = \frac{2u\sin(90^\circ-\theta)}{g} = \frac{2u\cos\theta}{g}$। গুণ করে: $t_1 t_2 = \frac{4u^2\sin\theta\cos\theta}{g^2} = \frac{2}{g}\left(\frac{u^2\sin 2\theta}{g}\right) = \frac{2R}{g}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>$H = 13.16\text{ m}, T = 3.28\text{ s}, R = 112.87\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>$t_1 t_2 = \frac{2R}{g}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5218,39 +4915,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 25</t>
+          <t>দ্বিমাত্রিক গতি ও প্রাসের সঞ্চারপথ (Oblique Projectile Kinematics)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $30^\circ$ কোণে $40\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+অনুভূমিকের সাথে $30^\circ$ কোণে একটি কামান থেকে $196	ext{ m/s}$ বেগে একটি গোলা ছোঁড়া হলো। নিক্ষেপের কত সময় পর গোলার বেগ অনুভূমিকের সাথে সমকোণে অবস্থান করবে? ($g = 9.8	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{40^2 \sin^2(30^\circ)}{2(9.8)} = 20.41\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.08\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 141.39\text{ m}$।</t>
+          <t>নিক্ষেপ ভেক্টর $\vec{u} = u\cos\theta\hat{i} + u\sin\theta\hat{j}$। $t$ সময় পর বেগ $\vec{v} = u\cos\theta\hat{i} + (u\sin\theta - gt)\hat{j}$। সমকোণে থাকার শর্ত $\vec{u} \cdot \vec{v} = 0 \implies u^2\cos^2\theta + u\sin\theta(u\sin\theta - gt) = 0 \implies u^2(\cos^2\theta + \sin^2\theta) = u gt\sin\theta \implies u^2 = u gt\sin\theta \implies t = \frac{u}{g\sin\theta} = \frac{196}{9.8\sin 30^\circ} = \frac{20}{0.5} = 40.0\text{ s}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>$H = 20.41\text{ m}, T = 4.08\text{ s}, R = 141.39\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>$t = 40.0\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5270,39 +4966,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 26</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $35^\circ$ কোণে $42\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=4.9,b=10,angle=26][size:small]##
+একটি পাহাড়ের চূড়া হতে $h = 490	ext{ m}$ উচ্চতা হতে একটি বোমা অনুভূমিকভাবে $100	ext{ m/s}$ বেগে ফেলে দেওয়া হলো ($g = 9.8	ext{ ms}^{-2}$)। বোমাটি কত সময় পর মাটিতে আঘাত করবে এবং এর আনুভূমিক দূরত্ব কত হবে?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=4.9,b=10,angle=26][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{42^2 \sin^2(35^\circ)}{2(9.8)} = 29.61\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.92\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 169.14\text{ m}$।</t>
+          <t>উল্লম্ব আদি বেগ শূন্য: $h = \frac{1}{2}g t^2 \implies 490 = 4.9 t^2 \implies t^2 = 100 \implies t = 10.0\text{ s}$। অনুভূমিক দূরত্ব $x = v_x \times t = 100 \times 10 = 1000\text{ m}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>$H = 29.61\text{ m}, T = 4.92\text{ s}, R = 169.14\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>সময় $t = 10.0\text{ s}$, আনুভূমিক দূরত্ব $x = 1000\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5322,39 +5017,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 27</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $40^\circ$ কোণে $44\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=4,b=6,angle=33][size:small]##
+একটি $80	ext{ m}$ উঁচু ভবনের ছাদ থেকে অনুভূমিকের সাথে $30^\circ$ কোণে উপরের দিকে $40	ext{ m/s}$ বেগে একটি পাথর ছোঁড়া হলো। পাথরটি কত সময় পর মাটিতে পৌঁছাবে এবং ভূমিতে আঘাত হানার মুহূর্তে এর দ্রুতি কত হবে? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=4,b=6,angle=33][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{44^2 \sin^2(40^\circ)}{2(9.8)} = 40.81\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 5.77\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 194.55\text{ m}$।</t>
+          <t>$u_x = 40\cos 30^\circ = 20\sqrt{3}\text{ m/s}$, $u_y = 40\sin 30^\circ = 20\text{ m/s}$। উল্লম্ব সরণ: $-80 = 20t - \frac{1}{2}(10)t^2 = 20t - 5t^2 \implies 5t^2 - 20t - 80 = 0 \implies t^2 - 4t - 16 = 0$। $t = \frac{4 \pm \sqrt{16 + 64}}{2} = \frac{4 + \sqrt{80}}{2} = \frac{4 + 8.944}{2} \approx 6.47\text{ s}$। শক্তির সংরক্ষণশীলতা অনুসারে ভূমিতে দ্রুতি: $v = \sqrt{u^2 + 2gh} = \sqrt{40^2 + 2(10)(80)} = \sqrt{1600 + 1600} = \sqrt{3200} \approx 56.57\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>$H = 40.81\text{ m}, T = 5.77\text{ s}, R = 194.55\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>সময় $t = 6.0\text{ s}$, আঘাতের দ্রুতি $v = 56.57\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5374,44 +5068,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 28</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $45^\circ$ কোণে $46\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:right-triangle[a=2,b=4,angle=26.5][size:small]##
+একটি বিমান অনুভূমিক সমতলে $720	ext{ km/h}$ দ্রুতিতে মাটি হতে $1960	ext{ m}$ উঁচুতে উড়ছে। ভূপৃষ্ঠের একটি নির্দিষ্ট লক্ষ্যে খাদ্য প্যাকেট ফেলতে হলে লক্ষ্যবস্তু হতে অনুভূমিকভাবে কত মিটার পূর্বে পাইলটকে প্যাকেটটি ড্রপ করতে হবে?</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##GEO:right-triangle[a=2,b=4,angle=26.5][size:small]##</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{46^2 \sin^2(45^\circ)}{2(9.8)} = 53.98\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.64\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 215.92\text{ m}$।</t>
+          <t>বেগ $v_x = \frac{720 \times 1000}{3600} = 200\text{ m/s}$। পতন কাল $h = \frac{1}{2}g t^2 \implies 1960 = 4.9 t^2 \implies t^2 = 400 \implies t = 20.0\text{ s}$। অনুভূমিক দূরত্ব $x = v_x t = 200 \times 20 = 4000\text{ m} = 4.0\text{ km}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>$H = 53.98\text{ m}, T = 6.64\text{ s}, R = 215.92\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>দূরত্ব $x = 4000\text{ m} = 4.0\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5431,39 +5119,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 29</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $50^\circ$ কোণে $48\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=3,b=3,c=4.24,angle=45][size:small]##
+একটি পাহাড়ের প্রান্ত হতে অনুভূমিকভাবে $v_0$ বেগে একটি পাথর নিক্ষেপ করা হলো। কত সময় পর পাথরের বেগ ভেক্টর অনুভূমিকের সাথে $45^\circ$ কোণ উৎপন্ন করবে?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=3,b=3,c=4.24,angle=45][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{48^2 \sin^2(50^\circ)}{2(9.8)} = 68.98\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 7.5\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 231.53\text{ m}$।</t>
+          <t>অনুভূমিক বেগ ধ্রুব: $v_x = v_0$। $t$ সময় পর নিম্নমুখী উল্লম্ব বেগ $v_y = gt$। কোণ $45^\circ$ হলে $\tan 45^\circ = \frac{v_y}{v_x} \implies 1 = \frac{gt}{v_0} \implies t = \frac{v_0}{g}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>$H = 68.98\text{ m}, T = 7.5\text{ s}, R = 231.53\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>$t = \frac{v_0}{g}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5483,39 +5170,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 30</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $55^\circ$ কোণে $20\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=2,b=8,angle=14][size:small]##
+একটি যুদ্ধজাহাজ হতে ভূমির সমতলে $200	ext{ m}$ উঁচু খাড়া পাহাড়ের ওপর থাকা একটি শত্রু ঘাঁটির দিকে কামান দাগা হলো। কামান ও ঘাঁটির মধ্যবর্তী অনুভূমিক দূরত্ব $800	ext{ m}$। কামানের নলের নিক্ষেপণ কোণ $45^\circ$ হলে প্রয়োজনীয় নূন্যতম আদি দ্রুতি কত হতে হবে? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=2,b=8,angle=14][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{20^2 \sin^2(55^\circ)}{2(9.8)} = 13.69\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.34\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 38.35\text{ m}$।</t>
+          <t>প্রাসের সমীকরণ: $y = x\tan\theta - \frac{g x^2}{2u^2\cos^2\theta}$। এখানে $x = 800\text{ m}, y = 200\text{ m}, \theta = 45^\circ$। $200 = 800\tan 45^\circ - \frac{10(800)^2}{2u^2(0.5)} = 800(1) - \frac{6400000}{u^2} \implies \frac{6400000}{u^2} = 600 \implies u^2 = \frac{6400000}{600} = \frac{64000}{6} \approx 10666.7 \implies u \approx 103.28\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>$H = 13.69\text{ m}, T = 3.34\text{ s}, R = 38.35\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>$u = 115.47\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5535,39 +5221,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 31</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $60^\circ$ কোণে $22\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি গাড়ি $v_0$ ধ্রুব দ্রুতিতে অনুভূমিক রাস্তায় চলছে। গাড়ির ছাদ থেকে খাড়া উপরের দিকে একটি বল নিক্ষেপ করা হলো। গাড়ির চালক এবং রাস্তায় দাঁড়িয়ে থাকা স্থির পর্যবেক্ষকের সাপেক্ষে বলটির গতিপথ কেমন দেখাবে?</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{22^2 \sin^2(60^\circ)}{2(9.8)} = 18.52\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.89\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 42.77\text{ m}$।</t>
+          <t>চালকের সাপেক্ষে বলটির কোনো অনুভূমিক আপেক্ষিক বেগ নেই ($v_{rel, x} = 0$), ফলে বলটি খাড়া উপরে উঠে পুনরায় চালকের হাতে ফিরে আসে (সরলরৈখিক উল্লম্ব গতি)। রাস্তায় স্থির ব্যক্তির সাপেক্ষে বলটির একটি অনুভূমিক বেগ $v_0$ এবং উল্লম্ব বেগ থাকে, ফলে গতিপথটি একটি দ্বি-মাত্রিক পরাবৃত্ত (Parabola) হবে।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>$H = 18.52\text{ m}, T = 3.89\text{ s}, R = 42.77\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>চালকের সাপেক্ষে সরলরৈখিক খাড়া উল্লম্ব, স্থির পর্যবেক্ষকের সাপেক্ষে পরাবৃত্তাকার (Parabolic)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5587,44 +5272,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 32</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $25^\circ$ কোণে $24\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি উঁচু টাওয়ারের শীর্ষ থেকে দুটি পাথর একই আদি বেগ $u = 20	ext{ m/s}$-এ নিক্ষেপ করা হলো; একটি অনুভূমিকের সাথে $30^\circ$ উপরে এবং অপরটি অনুভূমিকের সাথে $30^\circ$ নিচে। মাটিতে পৌঁছানোর সময়ের পার্থক্য নির্ণয় কর ($g = 10	ext{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{24^2 \sin^2(25^\circ)}{2(9.8)} = 5.25\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 2.07\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 45.02\text{ m}$।</t>
+          <t>উভয় পাথরের উল্লম্ব আদি বেগ যথাক্রমে $u_1 = +20\sin 30^\circ = +10\text{ m/s}$ এবং $u_2 = -20\sin 30^\circ = -10\text{ m/s}$। প্রথম পাথরটি উপরে গিয়ে আবার টাওয়ারের উচ্চতায় ফিরে আসতে সময় নেয় $\Delta t = \frac{2u_y}{g} = \frac{2(10)}{10} = 2.0\text{ s}$। এরপর উভয়ের গতি অভিন্ন হয়ে যায়। অতএব সময়ের পার্থক্য $\Delta t = 2.0\text{ s}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>$H = 5.25\text{ m}, T = 2.07\text{ s}, R = 45.02\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>সময়ের পার্থক্য $\Delta t = 2.0\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5644,39 +5323,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 33</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $30^\circ$ কোণে $26\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=2,b=2,c=2.83,angle=45][size:small]##
+ভূমি হতে $h = 20	ext{ m}$ উচ্চতায় উড়ন্ত একটি হেলিকপ্টার হতে অনুভূমিকভাবে একটি বস্তু ছোঁড়া হলো। বস্তুটি মাটিতে এমনভাবে আঘাত করে যে ভূমির সাথে স্পর্শক কোণ হয় $45^\circ$। বস্তুটির অনুভূমিক আদি বেগ কত ছিল? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=2,b=2,c=2.83,angle=45][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{26^2 \sin^2(30^\circ)}{2(9.8)} = 8.62\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 2.65\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 59.74\text{ m}$।</t>
+          <t>মাটিতে আঘাতের উল্লম্ব বেগ $v_y = \sqrt{2gh} = \sqrt{2(10)(20)} = \sqrt{400} = 20\text{ m/s}$। ভূমির সাথে কোণ $45^\circ$ হওয়ায় $\tan 45^\circ = \frac{v_y}{v_x} \implies 1 = \frac{20}{v_x} \implies v_x = 20.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>$H = 8.62\text{ m}, T = 2.65\text{ s}, R = 59.74\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>$v_x = 20.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5696,39 +5374,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 34</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $35^\circ$ কোণে $28\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=1.25,b=2.5,angle=26.5][size:small]##
+একটি টেবিলের উচ্চতা $1.25	ext{ m}$। টেবিল হতে গড়িয়ে পড়ে একটি মার্বেল টেবিলের পা হতে মেঝেতে $2.5	ext{ m}$ দূরে গিয়ে পড়ে। মার্বেলটি কত অনুভূমিক বেগে টেবিলের প্রান্ত ত্যাগ করেছিল? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=1.25,b=2.5,angle=26.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{28^2 \sin^2(35^\circ)}{2(9.8)} = 13.16\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.28\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 75.18\text{ m}$।</t>
+          <t>পতন কাল $h = \frac{1}{2}g t^2 \implies 1.25 = 5 t^2 \implies t^2 = 0.25 \implies t = 0.5\text{ s}$। অনুভূমিক বেগ $v_0 = \frac{x}{t} = \frac{2.5}{0.5} = 5.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>$H = 13.16\text{ m}, T = 3.28\text{ s}, R = 75.18\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>$v_0 = 5.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5748,39 +5425,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 35</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $40^\circ$ কোণে $30\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রক্ষেপককে এমন একটি কোণে নিক্ষেপ করা হলো যাতে তার সর্বোচ্চ উচ্চতায় বেগ আদি বেগের অর্ধেক ($v_{top} = u/2$) হয়। নিক্ষেপণ কোণ এবং অনুভূমিক পাল্লার সাথে সর্বোচ্চ উচ্চতার অনুপাত $R/H$ কত?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{30^2 \sin^2(40^\circ)}{2(9.8)} = 18.97\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.94\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 90.44\text{ m}$।</t>
+          <t>$v_{top} = u\cos\theta = u/2 \implies \cos\theta = 1/2 \implies \theta = 60^\circ$। $R = \frac{u^2\sin 120^\circ}{g} = \frac{\sqrt{3}u^2}{2g}$। $H = \frac{u^2\sin^2 60^\circ}{2g} = \frac{3u^2}{8g}$। অনুপাত $\frac{R}{H} = \frac{\sqrt{3}/2}{3/8} = \frac{4}{\sqrt{3}} \approx 2.31$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>$H = 18.97\text{ m}, T = 3.94\text{ s}, R = 90.44\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>$\theta = 60^\circ, R/H = \frac{4}{\sqrt{3}} \approx 2.31$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5800,44 +5476,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 36</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $45^\circ$ কোণে $32\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##
+একটি পাহাড়ের নতি কোণ $eta = 30^\circ$। পাহাড়ের ঢাল বরাবর উপরের দিকে অনুভূমিকের সাথে $lpha = 60^\circ$ কোণে $u = 30	ext{ m/s}$ বেগে একটি বস্তু ছোঁড়া হলো। ঢালের ওপর বস্তুর পাল্লা (Range on inclined plane) নির্ণয় কর ($g = 10	ext{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##GEO:right-triangle[a=3,b=5.2,angle=30][size:small]##</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{32^2 \sin^2(45^\circ)}{2(9.8)} = 26.12\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.62\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 104.49\text{ m}$।</t>
+          <t>ঢালের সাপেক্ষে আপেক্ষিক কোণ $\theta = \alpha - \beta = 60^\circ - 30^\circ = 30^\circ$। ঢালের ওপর পাল্লা: $R = \frac{u^2}{g\cos^2\beta}[\sin(2\theta+\beta) - \sin\beta] = \frac{900}{10(3/4)}[\sin 90^\circ - \sin 30^\circ] = \frac{900}{7.5}[1 - 0.5] = 120(0.5) = 60.0\text{ m}$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>$H = 26.12\text{ m}, T = 4.62\text{ s}, R = 104.49\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>$R_{inclined} = 60.0\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5857,39 +5527,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 37</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $50^\circ$ কোণে $34\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=2.5,b=4.3,angle=30][size:small]##
+একটি আনত তলের ওপর সর্বোচ্চ পাল্লা অর্জনের শর্ত প্রতিপাদন কর। দেখাও যে আনত তলের নতি কোণ $eta$ হলে ঢাল বরাবর উর্ধ্বমুখী সর্বোচ্চ পাল্লা $R_{\max} = rac{u^2}{g(1 + \sineta)}$।</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=2.5,b=4.3,angle=30][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{34^2 \sin^2(50^\circ)}{2(9.8)} = 34.61\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 5.32\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 116.17\text{ m}$।</t>
+          <t>পাল্লার সূত্র $R = \frac{u^2}{g\cos^2\beta}[\sin(2\theta+\beta) - \sin\beta]$। সর্বোচ্চ পাল্লার জন্য $\sin(2\theta+\beta) = 1 \implies 2\theta+\beta = 90^\circ \implies \theta = 45^\circ - \beta/2$। তখন $R_{\max} = \frac{u^2(1-\sin\beta)}{g\cos^2\beta} = \frac{u^2(1-\sin\beta)}{g(1-\sin^2\beta)} = \frac{u^2}{g(1+\sin\beta)}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>$H = 34.61\text{ m}, T = 5.32\text{ s}, R = 116.17\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>$R_{\max} = \frac{u^2}{g(1+\sin\beta)}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5909,39 +5578,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 38</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $55^\circ$ কোণে $36\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+দুটি বস্তুকে একই বিন্দু হতে একই দ্রুতি $u = 20	ext{ m/s}$-এ অনুভূমিকের সাথে যথাক্রমে $	heta_1 = 30^\circ$ এবং $	heta_2 = 60^\circ$ কোণে নিক্ষেপ করা হলো। নিক্ষেপের $1	ext{ সেকেন্ড}$ পর তাদের মধ্যকার সরলরৈখিক দূরত্ব কত? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{36^2 \sin^2(55^\circ)}{2(9.8)} = 44.37\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.02\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 124.27\text{ m}$।</t>
+          <t>প্রথম কণার অবস্থান: $x_1 = (20\cos 30^\circ)1 = 17.32\text{ m}, y_1 = (20\sin 30^\circ)1 - 5(1)^2 = 10 - 5 = 5\text{ m}$। দ্বিতীয় কণা: $x_2 = (20\cos 60^\circ)1 = 10\text{ m}, y_2 = (20\sin 60^\circ)1 - 5 = 17.32 - 5 = 12.32\text{ m}$। $\Delta x = 17.32 - 10 = 7.32\text{ m}, \Delta y = 5 - 12.32 = -7.32\text{ m}$। দূরত্ব $d = \sqrt{(7.32)^2 + (-7.32)^2} = 7.32\sqrt{2} \approx 10.35\text{ m}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>$H = 44.37\text{ m}, T = 6.02\text{ s}, R = 124.27\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>দূরত্ব $d = 10.35\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5961,39 +5629,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 39</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $60^\circ$ কোণে $38\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:right-triangle[a=5,b=5,angle=45][size:small]##
+একটি বন্দুক হতে অনুভূমিকের সাথে $45^\circ$ কোণে গুলি ছোঁড়ার মুহূর্তে $100	ext{ m}$ দূরে খাড়া গাছে থাকা একটি বানর ডাল ছেড়ে নিচে পড়ে গেল। দেখাও যে বানরটির পতন ত্বরণ অভিকর্ষীয় হওয়ায় গুলিটি বানরকে আঘাত করবে এবং আঘাতের উচ্চতা নির্ণয় কর যদি গুলির আদি বেগ $100	ext{ m/s}$ হয় ($g = 9.8	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:right-triangle[a=5,b=5,angle=45][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{38^2 \sin^2(60^\circ)}{2(9.8)} = 55.26\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.72\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 127.61\text{ m}$।</t>
+          <t>অনুভূমিক দূরত্ব $x = 100\text{ m}$। গুলির অনুভূমিক বেগ $u_x = 100\cos 45^\circ = 70.71\text{ m/s}$। সময় $t = \frac{100}{70.71} = 1.414\text{ s}$। বানরের পতন দূরত্ব $y_{fall} = \frac{1}{2}g t^2 = 4.9(2) = 9.8\text{ m}$। গাছের লক্ষ্যবিন্দুর আদি উচ্চতা $H = 100\tan 45^\circ = 100\text{ m}$। আঘাতের মুহূর্তে বানরের উচ্চতা $100 - 9.8 = 90.2\text{ m}$। গুলির উল্লম্ব উচ্চতা $y_{bullet} = u\sin 45^\circ t - \frac{1}{2}g t^2 = 70.71(1.414) - 9.8 = 100 - 9.8 = 90.2\text{ m}$। অতএব গুলি নিশ্চিতভাবে বানরকে আঘাত করবে।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>$H = 55.26\text{ m}, T = 6.72\text{ s}, R = 127.61\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>আঘাতের উচ্চতা $y = 90.2\text{ m}$, বানরকে আঘাত করবে</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6013,44 +5680,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 40</t>
+          <t>উঁচু স্থান হতে প্রক্ষেপক, আনত তলে প্রাস ও সংঘাত (Advanced Projectiles)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $25^\circ$ কোণে $40\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের গতিপথের সর্বোচ্চ উচ্চতা $H = 40	ext{ m}$। প্রাসটি নিক্ষেপণ বিন্দু হতে অনুভূমিকভাবে $x = 30	ext{ m}$ দূরত্বে $y = 30	ext{ m}$ উচ্চতায় থাকে। প্রাসটির আনুভূমিক পাল্লা $R$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{40^2 \sin^2(25^\circ)}{2(9.8)} = 14.58\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.45\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 125.07\text{ m}$।</t>
+          <t>প্রাসের গতিপথের রূপ: $y = x\tan\theta\left(1 - \frac{x}{R}\right)$ এবং $H = \frac{R\tan\theta}{4} \implies \tan\theta = \frac{4H}{R} = \frac{160}{R}$। বসিয়ে: $30 = 30\left(\frac{160}{R}\right)\left(1 - \frac{30}{R}\right) \implies 1 = \frac{160}{R}\left(1 - \frac{30}{R}\right) \implies R^2 - 160R + 4800 = 0$। দ্বিঘাত সমীকরণ হতে: $(R-120)(R-40) = 0$। যেহেতু $x = 30\text{ m}$ শীর্ষবিন্দুর পূর্বে এবং $H=40\text{ m}$ শীর্ষবিন্দু $x=R/2 &gt; 30 \implies R &gt; 60\text{ m}$। অতএব সঠিক পাল্লা $R = 120.0\text{ m}$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>$H = 14.58\text{ m}, T = 3.45\text{ s}, R = 125.07\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>পাল্লা $R = 120.0\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6070,39 +5731,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 41</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $30^\circ$ কোণে $42\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের অনুভূমিক সরণ $x = 6t$ এবং উল্লম্ব সরণ $y = 8t - 5t^2$ (যেখানে $x, y$ মিটারে এবং $t$ সেকেন্ডে)। প্রক্ষেপকটির আদি বেগ, নিক্ষেপণ কোণ এবং ১ সেকেন্ড পর বেগ ভেক্টরের মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{42^2 \sin^2(30^\circ)}{2(9.8)} = 22.5\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.29\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 155.88\text{ m}$।</t>
+          <t>$v_x = \frac{dx}{dt} = 6\text{ m/s}$ (ধ্রুব)। $v_y = \frac{dy}{dt} = 8 - 10t$। $t=0$-তে $u_x = 6, u_y = 8 \implies u = \sqrt{6^2+8^2} = 10\text{ m/s}$। কোণ $\tan\theta = \frac{8}{6} = \frac{4}{3} \implies \theta = 53.13^\circ$। $t = 1\text{ s}$-এ $v_y = 8 - 10 = -2\text{ m/s}$। দ্রুতি $v(1) = \sqrt{6^2 + (-2)^2} = \sqrt{36+4} = \sqrt{40} \approx 6.32\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>$H = 22.5\text{ m}, T = 4.29\text{ s}, R = 155.88\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>$u = 10.0\text{ m/s}, \theta = 53.13^\circ, v(1) = 6.32\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6122,39 +5782,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 42</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $35^\circ$ কোণে $44\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণা বৃত্তাকার পথে $r = 5	ext{ m}$ ব্যাসার্ধে এমনভাবে ঘুরছে যে তার রৈখিক বেগ সময়ের সাথে $v(t) = 3t^2	ext{ m/s}$ অনুসারে বাড়ে। $t = 2	ext{ s}$ মুহূর্তে কণাটির স্পর্শীয় ত্বরণ, কেন্দ্রমুখী ত্বরণ এবং লব্ধি ত্বরণ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{44^2 \sin^2(35^\circ)}{2(9.8)} = 32.5\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 5.15\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 185.64\text{ m}$।</t>
+          <t>স্পর্শীয় ত্বরণ $a_t = \frac{dv}{dt} = 6t$। $t = 2$-এ $a_t = 6(2) = 12\text{ m/s}^2$। দ্রুতি $v = 3(2)^2 = 12\text{ m/s}$। কেন্দ্রমুখী ত্বরণ $a_c = \frac{v^2}{r} = \frac{144}{5} = 28.8\text{ m/s}^2$। লব্ধি ত্বরণ $a = \sqrt{a_t^2 + a_c^2} = \sqrt{12^2 + (28.8)^2} = \sqrt{144 + 829.44} = \sqrt{973.44} \approx 31.20\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>$H = 32.5\text{ m}, T = 5.15\text{ s}, R = 185.64\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>$a_t = 12\text{ m/s}^2, a_c = 28.8\text{ m/s}^2, a = 31.2\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6174,39 +5833,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 43</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $40^\circ$ কোণে $46\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:rect[w=2,h=5][size:small]##
+একটি রকেট স্থির অবস্থা থেকে $20	ext{ m/s}^2$ ত্বরণে উল্লম্বভাবে উড্ডয়ন শুরু করল। $1	ext{ মিনিট}$ পর এর জ্বালানি শেষ হয়ে গেল। রকেটটি ভূপৃষ্ঠ হতে সর্বোচ্চ কত উচ্চতায় পৌঁছাবে? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{46^2 \sin^2(40^\circ)}{2(9.8)} = 44.61\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.03\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 212.64\text{ m}$।</t>
+          <t>$t_1 = 60\text{ s}$ পর রকেটের উচ্চতা $h_1 = \frac{1}{2}a t_1^2 = \frac{1}{2}(20)(3600) = 36000\text{ m} = 36\text{ km}$। অর্জিত বেগ $v = a t_1 = 20 \times 60 = 1200\text{ m/s}$। জ্বালানিহীন অবস্থায় মহাকর্ষের বিপরীতে অতিরিক্ত উচ্চতা $h_2 = \frac{v^2}{2g} = \frac{(1200)^2}{2(10)} = \frac{1440000}{20} = 72000\text{ m} = 72\text{ km}$। মোট সর্বোচ্চ উচ্চতা $H_{\max} = h_1 + h_2 = 36 + 72 = 108.0\text{ km}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>$H = 44.61\text{ m}, T = 6.03\text{ s}, R = 212.64\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>সর্বোচ্চ উচ্চতা $H_{\max} = 108.0\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6226,44 +5884,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 44</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $45^\circ$ কোণে $48\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি চাকার ব্যাসার্ধ $0.5	ext{ m}$। চাকাটি স্থির অবস্থা হতে সুষম কৌণিক ত্বরণ $lpha = 4	ext{ rad/s}^2$ নিয়ে ঘুরতে শুরু করল। $5	ext{ সেকেন্ড}$ পর চাকার পরিধির ওপর অবস্থিত একটি বিন্দুর রৈখিক বেগ এবং মোট ত্বরণ কত?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{48^2 \sin^2(45^\circ)}{2(9.8)} = 58.78\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 6.93\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 235.1\text{ m}$।</t>
+          <t>কৌণিক বেগ $\omega = \alpha t = 4 \times 5 = 20\text{ rad/s}$। রৈখিক বেগ $v = r\omega = 0.5 \times 20 = 10.0\text{ m/s}$। স্পর্শীয় ত্বরণ $a_t = r\alpha = 0.5 \times 4 = 2\text{ m/s}^2$। কেন্দ্রমুখী ত্বরণ $a_c = r\omega^2 = 0.5(400) = 200\text{ m/s}^2$। মোট ত্বরণ $a = \sqrt{a_t^2 + a_c^2} = \sqrt{2^2 + 200^2} = \sqrt{40004} \approx 200.01\text{ m/s}^2$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>$H = 58.78\text{ m}, T = 6.93\text{ s}, R = 235.1\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>$v = 10.0\text{ m/s}, a = 200.01\text{ m/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6283,39 +5935,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 45</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $50^\circ$ কোণে $20\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি উল্লম্ব বৃত্তাকার লুপের ব্যাসার্ধ $R = 2.5	ext{ m}$। লুপটির সর্বোচ্চ বিন্দুতে একটি ক্ষুদ্র ব্লকের পতনের ঝুঁকি না থাকার জন্য সর্বনিম্ন কত অনুভূমিক বেগ থাকতে হবে? ($g = 9.8	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{20^2 \sin^2(50^\circ)}{2(9.8)} = 11.98\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.13\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 40.2\text{ m}$।</t>
+          <t>সর্বোচ্চ বিন্দুতে মহাকর্ষ বলই কেন্দ্রমুখী বলের যোগান দেয় যখন তার প্রতিক্রিয়া বল শূন্য হয়: $mg = \frac{m v^2}{R} \implies v_{\min} = \sqrt{g R} = \sqrt{9.8 \times 2.5} = \sqrt{24.5} \approx 4.95\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>$H = 11.98\text{ m}, T = 3.13\text{ s}, R = 40.2\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>$v_{\min} = \sqrt{g R} = 4.95\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6335,39 +5986,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 46</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $55^\circ$ কোণে $22\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:trapezoid[a=2,b=4,h=2][size:small]##
+একটি কণার বেগ-সময় ($v-t$) লেখচিত্র একটি সমদ্বিবাহু ট্রাপিজিয়াম যার সমান্তরাল বাহুদ্বয় $t_1 = 10	ext{ s}$ ও $t_2 = 30	ext{ s}$ এবং উচ্চতা $v_{\max} = 15	ext{ m/s}$। কণাটির মোট অতিক্রান্ত দূরত্ব এবং গড় দ্রুতি কত?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:trapezoid[a=2,b=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{22^2 \sin^2(55^\circ)}{2(9.8)} = 16.57\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.68\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 46.41\text{ m}$।</t>
+          <t>ট্রাপিজিয়ামের ক্ষেত্রফল $= \frac{1}{2}(a+b)h = \frac{1}{2}(10 + 30) \times 15 = \frac{1}{2}(40)(15) = 300.0\text{ m}$। মোট সময় $T = 30\text{ s}$। গড় দ্রুতি $v_{avg} = \frac{s}{T} = \frac{300}{30} = 10.0\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>$H = 16.57\text{ m}, T = 3.68\text{ s}, R = 46.41\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>মোট দূরত্ব $s = 300.0\text{ m}$, গড় দ্রুতি $v_{avg} = 10.0\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6387,39 +6037,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 47</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $60^\circ$ কোণে $24\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=1.5][size:small]##
+একটি বন্দুক হতে অনুভূমিকভাবে প্রতি মিনিটে $600$ টি বুলেট ছোঁড়া হয়। প্রতিটি বুলেটের ভর $20	ext{ g}$ এবং বেগ $500	ext{ m/s}$ হলে বন্দুকটি স্থির ধরে রাখতে কত গড় বল প্রযুক্ত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{24^2 \sin^2(60^\circ)}{2(9.8)} = 22.04\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 4.24\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 50.9\text{ m}$।</t>
+          <t>প্রতি সেকেন্ডে বুলেটের সংখ্যা $n = \frac{600}{60} = 10\text{ s}^{-1}$। প্রতি সেকেন্ডে নির্গত ভর $\frac{dm}{dt} = 10 \times 0.020\text{ kg} = 0.20\text{ kg/s}$। নিউটনের দ্বিতীয় সূত্র অনুসারে ধাক্কা বল $F = \frac{dp}{dt} = v \frac{dm}{dt} = 500 \times 0.20 = 100.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>$H = 22.04\text{ m}, T = 4.24\text{ s}, R = 50.9\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>প্রযুক্ত বল $F = 100.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6439,44 +6088,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 48</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##
-একটি ফুটবলকে অনুভূমিকের সাথে $25^\circ$ কোণে $26\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:rect[w=4,h=1][size:small]##
+একটি কণার গতিশক্তি $K = 16 x^2$ জুল ($x$ অবস্থান মিটারে)। কণাটির ভর $2	ext{ kg}$ হলে $x = 3	ext{ m}$ অবস্থানে কণাটির ওপর প্রযুক্ত লব্ধি বলের মান কত?</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>##PRESET:projectile(45,20)[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=1][size:small]##</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{26^2 \sin^2(25^\circ)}{2(9.8)} = 6.16\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 2.24\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 52.84\text{ m}$।</t>
+          <t>$K = \frac{1}{2}m v^2 = 16x^2 \implies \frac{1}{2}(2)v^2 = 16x^2 \implies v^2 = 16x^2 \implies v = 4x$। ত্বরণ $a = v\frac{dv}{dx} = (4x)(4) = 16x$। বল $F = ma = 2(16x) = 32x$। $x = 3\text{ m}$-এ $F = 32(3) = 96.0\text{ N}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>$H = 6.16\text{ m}, T = 2.24\text{ s}, R = 52.84\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>$F = 96.0\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6496,39 +6139,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 49</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $30^\circ$ কোণে $28\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##PRESET:projectile-motion[size:medium]##
+একটি প্রাসের গতিপথের সর্বোচ্চ উচ্চতা $H = 25	ext{ m}$। যদি অনুভূমিক পাল্লা $R = 100	ext{ m}$ হয়, তবে প্রক্ষেপকটির বায়ুতে বিচরণকাল $T$ কত? ($g = 10	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##PRESET:projectile-motion[size:medium]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{28^2 \sin^2(30^\circ)}{2(9.8)} = 10.0\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 2.86\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 69.28\text{ m}$।</t>
+          <t>$H = \frac{u_y^2}{2g} \implies 25 = \frac{u_y^2}{20} \implies u_y^2 = 500 \implies u_y = \sqrt{500} = 10\sqrt{5} \approx 22.36\text{ m/s}$। বিচরণকাল $T = \frac{2u_y}{g} = \frac{2(22.36)}{10} \approx 4.47\text{ s}$ (সঠিক হিসাব: $T = 2\sqrt{\frac{2H}{g}} = 2\sqrt{\frac{50}{10}} = 2\sqrt{5} \approx 4.47\text{ s}$)।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>$H = 10.0\text{ m}, T = 2.86\text{ s}, R = 69.28\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$T = 3.16\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6548,39 +6190,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>প্রাসের বিচরণকাল ও পাল্লা বিশ্লেষণ 50</t>
+          <t>উন্নত গতিবিদ্যা ও গতিশক্তি-বল সম্পর্ক (Advanced Dynamics &amp; Calculus)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>একটি ফুটবলকে অনুভূমিকের সাথে $35^\circ$ কোণে $30\text{ m/s}$ বেগে কিক করা হলো। বলটির সর্বোচ্চ উচ্চতা, বিচরণকাল এবং অনুভূমিক পাল্লা নির্ণয় কর। ($g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:rect[w=2,h=5][size:small]##
+একটি অবাধে পতনশীল বস্তু শেষ সেকেন্ডে তার মোট পতনের দূরত্বের $9/25$ অংশ অতিক্রম করে। বস্তুটি কত উচ্চতা হতে পতিত হয়েছিল এবং মোট পতনকাল কত? ($g = 9.8	ext{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=2,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>সর্বোচ্চ উচ্চতা $H = \frac{v_0^2 \sin^2\theta}{2g} = \frac{30^2 \sin^2(35^\circ)}{2(9.8)} = 15.11\text{ m}$।
-বিচরণকাল $T = \frac{2v_0\sin\theta}{g} = 3.51\text{ s}$।
-পাল্লা $R = \frac{v_0^2 \sin(2\theta)}{g} = 86.3\text{ m}$।</t>
+          <t>মোট উচ্চতা $h = \frac{1}{2}g t^2$। $(t-1)$ সেকেন্ডে অতিক্রান্ত উচ্চতা $h' = \frac{1}{2}g (t-1)^2$। শেষ সেকেন্ডে সরণ $s_t = h - h' = \frac{9}{25}h \implies h' = \frac{16}{25}h \implies \frac{(t-1)^2}{t^2} = \frac{16}{25} \implies \frac{t-1}{t} = \frac{4}{5} \implies 5t - 5 = 4t \implies t = 5.0\text{ s}$। মোট উচ্চতা $h = \frac{1}{2}(9.8)(5)^2 = 4.9 \times 25 = 122.5\text{ m}$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>$H = 15.11\text{ m}, T = 3.51\text{ s}, R = 86.3\text{ m}$</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>পতনকাল $t = 5.0\text{ s}$, উচ্চতা $h = 122.5\text{ m}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
